--- a/MU.xlsx
+++ b/MU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE994E08-B983-4B72-81F0-4CFD558B0142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7076C5-5BE9-4C94-A016-294804C3D541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45390" yWindow="585" windowWidth="34620" windowHeight="19830" activeTab="1" xr2:uid="{040A5584-314E-40E5-8C54-C0576405A9F8}"/>
+    <workbookView xWindow="12160" yWindow="3160" windowWidth="22360" windowHeight="13220" xr2:uid="{040A5584-314E-40E5-8C54-C0576405A9F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="159">
   <si>
     <t>Price</t>
   </si>
@@ -520,6 +520,18 @@
   </si>
   <si>
     <t>R FCF</t>
+  </si>
+  <si>
+    <t>FQ126</t>
+  </si>
+  <si>
+    <t>FQ226</t>
+  </si>
+  <si>
+    <t>FQ326</t>
+  </si>
+  <si>
+    <t>FQ426</t>
   </si>
 </sst>
 </file>
@@ -527,9 +539,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -548,12 +560,6 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -596,15 +602,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -624,27 +630,19 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -703,7 +701,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Model!$AH$2:$AZ$2</c:f>
+              <c:f>Model!$AL$2:$BD$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yy;@</c:formatCode>
                 <c:ptCount val="19"/>
@@ -762,14 +760,14 @@
                   <c:v>45169</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>45535</c:v>
+                  <c:v>45533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$AH$63:$AZ$63</c:f>
+              <c:f>Model!$AL$63:$BD$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -873,7 +871,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Model!$AH$2:$AZ$2</c:f>
+              <c:f>Model!$AL$2:$BD$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yy;@</c:formatCode>
                 <c:ptCount val="19"/>
@@ -932,14 +930,14 @@
                   <c:v>45169</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>45535</c:v>
+                  <c:v>45533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$AH$54:$AZ$54</c:f>
+              <c:f>Model!$AL$54:$BD$54</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="19"/>
@@ -1183,6 +1181,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1561041119"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -1197,6 +1196,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1204,7 +1204,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1306,7 +1305,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Model!$AD$2:$AZ$2</c:f>
+              <c:f>Model!$AH$2:$BD$2</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yy;@</c:formatCode>
                 <c:ptCount val="23"/>
@@ -1377,14 +1376,14 @@
                   <c:v>45169</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>45535</c:v>
+                  <c:v>45533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$AD$65:$AZ$65</c:f>
+              <c:f>Model!$AH$65:$BD$65</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="23"/>
@@ -1455,7 +1454,7 @@
                   <c:v>182.09514881649869</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>277.34444444444443</c:v>
+                  <c:v>279.01111111111112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1595,6 +1594,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1602,7 +1602,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2753,16 +2752,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>20266</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>44689</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>68617</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>20266</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>44689</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>108262</xdr:rowOff>
+      <xdr:rowOff>39645</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2777,8 +2776,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7680371" y="68617"/>
-          <a:ext cx="0" cy="8060698"/>
+          <a:off x="12397881" y="0"/>
+          <a:ext cx="0" cy="9120145"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2803,13 +2802,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>40</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>302950</xdr:colOff>
       <xdr:row>66</xdr:row>
       <xdr:rowOff>5376</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>50</xdr:col>
+      <xdr:col>54</xdr:col>
       <xdr:colOff>109944</xdr:colOff>
       <xdr:row>86</xdr:row>
       <xdr:rowOff>74852</xdr:rowOff>
@@ -2839,13 +2838,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>164855</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>21986</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>479913</xdr:colOff>
       <xdr:row>85</xdr:row>
       <xdr:rowOff>24917</xdr:rowOff>
@@ -3208,20 +3207,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E54B3D3-F24B-4B90-87C3-03D13C01C91B}">
   <dimension ref="B2:K12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="18" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="16" t="s">
         <v>106</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>89</v>
+        <v>587</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>107</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>108</v>
       </c>
@@ -3244,10 +3243,10 @@
       </c>
       <c r="J4" s="2">
         <f>+J2*J3</f>
-        <v>98686.878014000002</v>
+        <v>650889.85836199997</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>111</v>
       </c>
@@ -3262,7 +3261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>112</v>
       </c>
@@ -3277,7 +3276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>109</v>
       </c>
@@ -3286,25 +3285,25 @@
       </c>
       <c r="J7" s="2">
         <f>+J4-J5+J6</f>
-        <v>102790.878014</v>
+        <v>654993.85836199997</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I9" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>114</v>
       </c>
@@ -3316,21 +3315,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC95ECE1-E2C2-4F5D-AB90-79F4AAA15D0A}">
-  <dimension ref="A1:CR68"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:CV68"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="3"/>
-    <col min="44" max="44" width="9.140625" style="3"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="3"/>
+    <col min="48" max="48" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:96" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:100" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5">
@@ -3361,136 +3360,151 @@
         <f>+I2+366</f>
         <v>45535</v>
       </c>
-      <c r="N2" s="5"/>
-      <c r="W2" s="4">
-        <f t="shared" ref="W2:Z2" si="0">+X2-365</f>
+      <c r="N2" s="5">
+        <v>45624</v>
+      </c>
+      <c r="O2" s="4">
+        <v>45715</v>
+      </c>
+      <c r="P2" s="4">
+        <f>+L2+365</f>
+        <v>45807</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>45897</v>
+      </c>
+      <c r="R2" s="4">
+        <v>45988</v>
+      </c>
+      <c r="S2" s="4">
+        <v>46079</v>
+      </c>
+      <c r="AA2" s="4">
+        <f t="shared" ref="AA2:AC2" si="0">+AB2-365</f>
         <v>34948</v>
       </c>
-      <c r="X2" s="4">
+      <c r="AB2" s="4">
         <f t="shared" si="0"/>
         <v>35313</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="AC2" s="4">
         <f t="shared" si="0"/>
         <v>35678</v>
       </c>
-      <c r="Z2" s="4">
-        <f t="shared" ref="Z2:AD2" si="1">+AA2-365</f>
+      <c r="AD2" s="4">
+        <f t="shared" ref="AD2:AG2" si="1">+AE2-365</f>
         <v>36043</v>
       </c>
-      <c r="AA2" s="4">
+      <c r="AE2" s="4">
         <f t="shared" si="1"/>
         <v>36408</v>
       </c>
-      <c r="AB2" s="4">
+      <c r="AF2" s="4">
         <f t="shared" si="1"/>
         <v>36773</v>
       </c>
-      <c r="AC2" s="4">
+      <c r="AG2" s="4">
         <f t="shared" si="1"/>
         <v>37138</v>
       </c>
-      <c r="AD2" s="4">
-        <f>+AE2-365</f>
+      <c r="AH2" s="4">
+        <f t="shared" ref="AH2:AP2" si="2">+AI2-365</f>
         <v>37503</v>
       </c>
-      <c r="AE2" s="4">
-        <f>+AF2-365</f>
+      <c r="AI2" s="4">
+        <f t="shared" si="2"/>
         <v>37868</v>
       </c>
-      <c r="AF2" s="4">
-        <f>+AG2-365</f>
+      <c r="AJ2" s="4">
+        <f t="shared" si="2"/>
         <v>38233</v>
       </c>
-      <c r="AG2" s="4">
-        <f>+AH2-365</f>
+      <c r="AK2" s="4">
+        <f t="shared" si="2"/>
         <v>38598</v>
       </c>
-      <c r="AH2" s="4">
-        <f>+AI2-365</f>
+      <c r="AL2" s="4">
+        <f t="shared" si="2"/>
         <v>38963</v>
       </c>
-      <c r="AI2" s="4">
-        <f>+AJ2-365</f>
+      <c r="AM2" s="4">
+        <f t="shared" si="2"/>
         <v>39328</v>
       </c>
-      <c r="AJ2" s="4">
-        <f>+AK2-365</f>
+      <c r="AN2" s="4">
+        <f t="shared" si="2"/>
         <v>39693</v>
       </c>
-      <c r="AK2" s="4">
-        <f>+AL2-365</f>
+      <c r="AO2" s="4">
+        <f t="shared" si="2"/>
         <v>40058</v>
       </c>
-      <c r="AL2" s="4">
-        <f>+AM2-365</f>
+      <c r="AP2" s="4">
+        <f t="shared" si="2"/>
         <v>40423</v>
       </c>
-      <c r="AM2" s="5">
-        <f t="shared" ref="AM2:AP2" si="2">+AN2-365</f>
+      <c r="AQ2" s="5">
+        <f t="shared" ref="AQ2:AS2" si="3">+AR2-365</f>
         <v>40788</v>
       </c>
-      <c r="AN2" s="5">
-        <f t="shared" si="2"/>
+      <c r="AR2" s="5">
+        <f t="shared" si="3"/>
         <v>41153</v>
       </c>
-      <c r="AO2" s="5">
-        <f t="shared" si="2"/>
+      <c r="AS2" s="5">
+        <f t="shared" si="3"/>
         <v>41518</v>
       </c>
-      <c r="AP2" s="5">
-        <f t="shared" ref="AP2:AR2" si="3">+AQ2-365</f>
+      <c r="AT2" s="5">
+        <f t="shared" ref="AT2:AU2" si="4">+AU2-365</f>
         <v>41883</v>
       </c>
-      <c r="AQ2" s="5">
-        <f t="shared" si="3"/>
+      <c r="AU2" s="5">
+        <f t="shared" si="4"/>
         <v>42248</v>
       </c>
-      <c r="AR2" s="5">
-        <f>+AS2-365</f>
+      <c r="AV2" s="5">
+        <f>+AW2-365</f>
         <v>42613</v>
       </c>
-      <c r="AS2" s="4">
+      <c r="AW2" s="4">
         <v>42978</v>
       </c>
-      <c r="AT2" s="4">
+      <c r="AX2" s="4">
         <v>43342</v>
       </c>
-      <c r="AU2" s="4">
+      <c r="AY2" s="4">
         <v>43706</v>
       </c>
-      <c r="AV2" s="4">
-        <f>+AW2-365</f>
+      <c r="AZ2" s="4">
+        <f>+BA2-365</f>
         <v>44076</v>
       </c>
-      <c r="AW2" s="4">
+      <c r="BA2" s="4">
         <v>44441</v>
       </c>
-      <c r="AX2" s="4">
+      <c r="BB2" s="4">
         <v>44805</v>
       </c>
-      <c r="AY2" s="4">
-        <f>+I2</f>
+      <c r="BC2" s="4">
         <v>45169</v>
       </c>
-      <c r="AZ2" s="4">
-        <f>+M2</f>
-        <v>45535</v>
-      </c>
-      <c r="BA2" s="4">
-        <f>+AZ2+365</f>
-        <v>45900</v>
-      </c>
-      <c r="BB2" s="4">
-        <f>+BA2+365</f>
-        <v>46265</v>
-      </c>
-      <c r="BC2" s="4">
-        <f>+BB2+365</f>
-        <v>46630</v>
+      <c r="BD2" s="4">
+        <v>45533</v>
+      </c>
+      <c r="BE2" s="4">
+        <v>45897</v>
+      </c>
+      <c r="BF2" s="4">
+        <f>+BE2+365</f>
+        <v>46262</v>
+      </c>
+      <c r="BG2" s="4">
+        <f>+BF2+365</f>
+        <v>46627</v>
       </c>
     </row>
-    <row r="3" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:100" x14ac:dyDescent="0.25">
       <c r="E3" s="3" t="s">
         <v>34</v>
       </c>
@@ -3530,243 +3544,255 @@
       <c r="Q3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="3"/>
+      <c r="R3" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="S3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="Y3" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="AA3" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="AB3" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AK3" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AM3" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AN3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AO3" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AP3" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AQ3" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AN3" s="3" t="s">
+      <c r="AR3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AO3" s="3" t="s">
+      <c r="AS3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="AP3" s="3" t="s">
+      <c r="AT3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="AQ3" s="3" t="s">
+      <c r="AU3" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="AR3" s="3" t="s">
+      <c r="AV3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="AS3" s="3" t="s">
+      <c r="AW3" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AX3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="AU3" s="3" t="s">
+      <c r="AY3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="AV3" s="3" t="s">
+      <c r="AZ3" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AW3" s="3" t="s">
+      <c r="BA3" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AX3" s="3" t="s">
+      <c r="BB3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AY3" s="3" t="s">
+      <c r="BC3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AZ3" s="3" t="s">
+      <c r="BD3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BA3" s="3" t="s">
+      <c r="BE3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BB3" s="3" t="s">
+      <c r="BF3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BC3" s="3" t="s">
+      <c r="BG3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BD3" s="3" t="s">
+      <c r="BH3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="BE3" s="3" t="s">
+      <c r="BI3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BF3" s="3" t="s">
+      <c r="BJ3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BG3" s="3" t="s">
+      <c r="BK3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="BH3" s="3" t="s">
+      <c r="BL3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BI3" s="3" t="s">
+      <c r="BM3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="BJ3" s="3" t="s">
+      <c r="BN3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="BK3" s="3" t="s">
+      <c r="BO3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="BL3" s="3" t="s">
+      <c r="BP3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BM3" s="3" t="s">
+      <c r="BQ3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="BN3" s="3" t="s">
+      <c r="BR3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="BO3" s="3" t="s">
+      <c r="BS3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="BP3" s="3" t="s">
+      <c r="BT3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="BQ3" s="3" t="s">
+      <c r="BU3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="BR3" s="3" t="s">
+      <c r="BV3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="3" t="s">
+      <c r="BW3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="BT3" s="3" t="s">
+      <c r="BX3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="BU3" s="3" t="s">
+      <c r="BY3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="BV3" s="3" t="s">
+      <c r="BZ3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="BW3" s="3" t="s">
+      <c r="CA3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="BX3" s="3" t="s">
+      <c r="CB3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="BY3" s="3" t="s">
+      <c r="CC3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="BZ3" s="3" t="s">
+      <c r="CD3" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="CA3" s="3" t="s">
+      <c r="CE3" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="CB3" s="3" t="s">
+      <c r="CF3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="CC3" s="3" t="s">
+      <c r="CG3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="CD3" s="3" t="s">
+      <c r="CH3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="CE3" s="3" t="s">
+      <c r="CI3" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="CF3" s="3" t="s">
+      <c r="CJ3" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="CG3" s="3" t="s">
+      <c r="CK3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="CH3" s="3" t="s">
+      <c r="CL3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="CI3" s="3" t="s">
+      <c r="CM3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="CJ3" s="3" t="s">
+      <c r="CN3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="CK3" s="3" t="s">
+      <c r="CO3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="CL3" s="3" t="s">
+      <c r="CP3" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="CM3" s="3" t="s">
+      <c r="CQ3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="CN3" s="3" t="s">
+      <c r="CR3" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="CO3" s="3" t="s">
+      <c r="CS3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="CP3" s="3" t="s">
+      <c r="CT3" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="CQ3" s="3" t="s">
+      <c r="CU3" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="CR3" s="3" t="s">
+      <c r="CV3" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:100" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>113</v>
       </c>
@@ -3799,24 +3825,24 @@
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
       <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
       <c r="AT4" s="3"/>
       <c r="AU4" s="3"/>
-      <c r="AV4" s="14">
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="AZ4" s="6">
         <v>9184</v>
       </c>
-      <c r="AW4" s="14">
+      <c r="BA4" s="6">
         <v>12280</v>
       </c>
-      <c r="AX4" s="14">
+      <c r="BB4" s="6">
         <v>13693</v>
       </c>
-      <c r="AY4" s="14">
+      <c r="BC4" s="6">
         <v>5710</v>
       </c>
-      <c r="AZ4" s="3"/>
-      <c r="BA4" s="3"/>
-      <c r="BB4" s="3"/>
-      <c r="BC4" s="3"/>
       <c r="BD4" s="3"/>
       <c r="BE4" s="3"/>
       <c r="BF4" s="3"/>
@@ -3858,8 +3884,12 @@
       <c r="CP4" s="3"/>
       <c r="CQ4" s="3"/>
       <c r="CR4" s="3"/>
+      <c r="CS4" s="3"/>
+      <c r="CT4" s="3"/>
+      <c r="CU4" s="3"/>
+      <c r="CV4" s="3"/>
     </row>
-    <row r="5" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:100" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>115</v>
       </c>
@@ -3892,24 +3922,24 @@
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
       <c r="AQ5" s="3"/>
+      <c r="AR5" s="3"/>
+      <c r="AS5" s="3"/>
       <c r="AT5" s="3"/>
       <c r="AU5" s="3"/>
-      <c r="AV5" s="6">
+      <c r="AX5" s="3"/>
+      <c r="AY5" s="3"/>
+      <c r="AZ5" s="6">
         <v>5702</v>
       </c>
-      <c r="AW5" s="6">
+      <c r="BA5" s="6">
         <v>7203</v>
       </c>
-      <c r="AX5" s="6">
+      <c r="BB5" s="6">
         <v>7260</v>
       </c>
-      <c r="AY5" s="6">
+      <c r="BC5" s="6">
         <v>3630</v>
       </c>
-      <c r="AZ5" s="3"/>
-      <c r="BA5" s="3"/>
-      <c r="BB5" s="3"/>
-      <c r="BC5" s="3"/>
       <c r="BD5" s="3"/>
       <c r="BE5" s="3"/>
       <c r="BF5" s="3"/>
@@ -3951,8 +3981,12 @@
       <c r="CP5" s="3"/>
       <c r="CQ5" s="3"/>
       <c r="CR5" s="3"/>
+      <c r="CS5" s="3"/>
+      <c r="CT5" s="3"/>
+      <c r="CU5" s="3"/>
+      <c r="CV5" s="3"/>
     </row>
-    <row r="6" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:100" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>116</v>
       </c>
@@ -3985,24 +4019,24 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
       <c r="AQ6" s="3"/>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="3"/>
       <c r="AT6" s="3"/>
       <c r="AU6" s="3"/>
-      <c r="AV6" s="6">
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+      <c r="AZ6" s="6">
         <v>2759</v>
       </c>
-      <c r="AW6" s="6">
+      <c r="BA6" s="6">
         <v>4209</v>
       </c>
-      <c r="AX6" s="6">
+      <c r="BB6" s="6">
         <v>5235</v>
       </c>
-      <c r="AY6" s="6">
+      <c r="BC6" s="6">
         <v>3640</v>
       </c>
-      <c r="AZ6" s="3"/>
-      <c r="BA6" s="3"/>
-      <c r="BB6" s="3"/>
-      <c r="BC6" s="3"/>
       <c r="BD6" s="3"/>
       <c r="BE6" s="3"/>
       <c r="BF6" s="3"/>
@@ -4044,8 +4078,12 @@
       <c r="CP6" s="3"/>
       <c r="CQ6" s="3"/>
       <c r="CR6" s="3"/>
+      <c r="CS6" s="3"/>
+      <c r="CT6" s="3"/>
+      <c r="CU6" s="3"/>
+      <c r="CV6" s="3"/>
     </row>
-    <row r="7" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:100" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>117</v>
       </c>
@@ -4078,24 +4116,24 @@
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
       <c r="AQ7" s="3"/>
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="3"/>
       <c r="AT7" s="3"/>
       <c r="AU7" s="3"/>
-      <c r="AV7" s="6">
+      <c r="AX7" s="3"/>
+      <c r="AY7" s="3"/>
+      <c r="AZ7" s="6">
         <v>3765</v>
       </c>
-      <c r="AW7" s="6">
+      <c r="BA7" s="6">
         <v>3973</v>
       </c>
-      <c r="AX7" s="6">
+      <c r="BB7" s="6">
         <v>4553</v>
       </c>
-      <c r="AY7" s="6">
+      <c r="BC7" s="6">
         <v>2550</v>
       </c>
-      <c r="AZ7" s="3"/>
-      <c r="BA7" s="3"/>
-      <c r="BB7" s="3"/>
-      <c r="BC7" s="3"/>
       <c r="BD7" s="3"/>
       <c r="BE7" s="3"/>
       <c r="BF7" s="3"/>
@@ -4137,8 +4175,12 @@
       <c r="CP7" s="3"/>
       <c r="CQ7" s="3"/>
       <c r="CR7" s="3"/>
+      <c r="CS7" s="3"/>
+      <c r="CT7" s="3"/>
+      <c r="CU7" s="3"/>
+      <c r="CV7" s="3"/>
     </row>
-    <row r="8" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:100" x14ac:dyDescent="0.25">
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -4168,24 +4210,24 @@
       <c r="AO8" s="3"/>
       <c r="AP8" s="3"/>
       <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
       <c r="AT8" s="3"/>
       <c r="AU8" s="3"/>
-      <c r="AV8" s="6">
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+      <c r="AZ8" s="6">
         <v>25</v>
       </c>
-      <c r="AW8" s="3">
+      <c r="BA8" s="3">
         <v>40</v>
       </c>
-      <c r="AX8" s="3">
+      <c r="BB8" s="3">
         <v>17</v>
       </c>
-      <c r="AY8" s="3">
+      <c r="BC8" s="3">
         <v>10</v>
       </c>
-      <c r="AZ8" s="3"/>
-      <c r="BA8" s="3"/>
-      <c r="BB8" s="3"/>
-      <c r="BC8" s="3"/>
       <c r="BD8" s="3"/>
       <c r="BE8" s="3"/>
       <c r="BF8" s="3"/>
@@ -4227,8 +4269,12 @@
       <c r="CP8" s="3"/>
       <c r="CQ8" s="3"/>
       <c r="CR8" s="3"/>
+      <c r="CS8" s="3"/>
+      <c r="CT8" s="3"/>
+      <c r="CU8" s="3"/>
+      <c r="CV8" s="3"/>
     </row>
-    <row r="9" spans="1:96" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:100" x14ac:dyDescent="0.25">
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -4258,10 +4304,10 @@
       <c r="AO9" s="3"/>
       <c r="AP9" s="3"/>
       <c r="AQ9" s="3"/>
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="3"/>
       <c r="AT9" s="3"/>
       <c r="AU9" s="3"/>
-      <c r="AV9" s="3"/>
-      <c r="AW9" s="3"/>
       <c r="AX9" s="3"/>
       <c r="AY9" s="3"/>
       <c r="AZ9" s="3"/>
@@ -4309,8 +4355,12 @@
       <c r="CP9" s="3"/>
       <c r="CQ9" s="3"/>
       <c r="CR9" s="3"/>
+      <c r="CS9" s="3"/>
+      <c r="CT9" s="3"/>
+      <c r="CU9" s="3"/>
+      <c r="CV9" s="3"/>
     </row>
-    <row r="10" spans="1:96" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:100" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
@@ -4341,85 +4391,107 @@
         <v>6811</v>
       </c>
       <c r="M10" s="10">
-        <v>7600</v>
-      </c>
-      <c r="N10" s="10"/>
-      <c r="AD10" s="9">
+        <f>25111-L10-K10-J10</f>
+        <v>7750</v>
+      </c>
+      <c r="N10" s="9">
+        <v>8709</v>
+      </c>
+      <c r="O10" s="9">
+        <v>8053</v>
+      </c>
+      <c r="P10" s="9">
+        <v>9301</v>
+      </c>
+      <c r="Q10" s="9">
+        <f>+BE10-P10-O10-N10</f>
+        <v>11315</v>
+      </c>
+      <c r="R10" s="9">
+        <v>13643</v>
+      </c>
+      <c r="S10" s="9">
+        <v>23860</v>
+      </c>
+      <c r="AH10" s="9">
         <v>2589</v>
       </c>
-      <c r="AE10" s="9">
+      <c r="AI10" s="9">
         <v>3091</v>
       </c>
-      <c r="AF10" s="9">
+      <c r="AJ10" s="9">
         <v>4404</v>
       </c>
-      <c r="AG10" s="9">
+      <c r="AK10" s="9">
         <v>4880</v>
       </c>
-      <c r="AH10" s="9">
+      <c r="AL10" s="9">
         <v>5272</v>
       </c>
-      <c r="AI10" s="9">
+      <c r="AM10" s="9">
         <v>5688</v>
       </c>
-      <c r="AJ10" s="9">
+      <c r="AN10" s="9">
         <v>5841</v>
       </c>
-      <c r="AK10" s="9">
+      <c r="AO10" s="9">
         <v>4803</v>
       </c>
-      <c r="AL10" s="9">
+      <c r="AP10" s="9">
         <v>8482</v>
       </c>
-      <c r="AM10" s="9">
+      <c r="AQ10" s="9">
         <v>8788</v>
       </c>
-      <c r="AN10" s="9">
+      <c r="AR10" s="9">
         <v>8234</v>
       </c>
-      <c r="AO10" s="9">
+      <c r="AS10" s="9">
         <v>9073</v>
       </c>
-      <c r="AP10" s="9">
+      <c r="AT10" s="9">
         <v>16358</v>
       </c>
-      <c r="AQ10" s="9">
+      <c r="AU10" s="9">
         <v>16192</v>
       </c>
-      <c r="AR10" s="10">
+      <c r="AV10" s="10">
         <v>12399</v>
       </c>
-      <c r="AS10" s="9">
+      <c r="AW10" s="9">
         <v>20322</v>
       </c>
-      <c r="AT10" s="9">
+      <c r="AX10" s="9">
         <v>30391</v>
       </c>
-      <c r="AU10" s="9">
+      <c r="AY10" s="9">
         <v>23406</v>
       </c>
-      <c r="AV10" s="9">
-        <f>SUM(AV4:AV8)</f>
+      <c r="AZ10" s="9">
+        <f>SUM(AZ4:AZ8)</f>
         <v>21435</v>
       </c>
-      <c r="AW10" s="9">
-        <f>SUM(AW4:AW8)</f>
+      <c r="BA10" s="9">
+        <f>SUM(BA4:BA8)</f>
         <v>27705</v>
       </c>
-      <c r="AX10" s="9">
-        <f>SUM(AX4:AX8)</f>
+      <c r="BB10" s="9">
+        <f>SUM(BB4:BB8)</f>
         <v>30758</v>
       </c>
-      <c r="AY10" s="9">
-        <f>SUM(AY4:AY8)</f>
+      <c r="BC10" s="9">
+        <f>SUM(BC4:BC8)</f>
         <v>15540</v>
       </c>
-      <c r="AZ10" s="9">
+      <c r="BD10" s="9">
         <f>SUM(J10:M10)</f>
-        <v>24961</v>
+        <v>25111</v>
+      </c>
+      <c r="BE10" s="9">
+        <v>37378</v>
       </c>
     </row>
-    <row r="11" spans="1:96" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:100" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
@@ -4449,154 +4521,214 @@
       <c r="L11" s="6">
         <v>4979</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="AP11" s="2">
+      <c r="M11" s="6">
+        <f>19498-L11-K11-J11</f>
+        <v>5013</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5361</v>
+      </c>
+      <c r="O11" s="2">
+        <v>5090</v>
+      </c>
+      <c r="P11" s="2">
+        <v>5793</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>+BE11-P11-O11-N11</f>
+        <v>6261</v>
+      </c>
+      <c r="R11" s="2">
+        <v>5997</v>
+      </c>
+      <c r="S11" s="2">
+        <v>6105</v>
+      </c>
+      <c r="AT11" s="2">
         <v>10921</v>
       </c>
-      <c r="AQ11" s="2">
+      <c r="AU11" s="2">
         <v>10977</v>
       </c>
-      <c r="AR11" s="6">
+      <c r="AV11" s="6">
         <v>9894</v>
       </c>
-      <c r="AS11" s="2">
+      <c r="AW11" s="2">
         <v>11886</v>
       </c>
-      <c r="AT11" s="2">
+      <c r="AX11" s="2">
         <v>12500</v>
       </c>
-      <c r="AU11" s="2">
+      <c r="AY11" s="2">
         <v>12704</v>
       </c>
-      <c r="AV11" s="2">
+      <c r="AZ11" s="2">
         <v>14883</v>
       </c>
-      <c r="AW11" s="2">
+      <c r="BA11" s="2">
         <v>17282</v>
       </c>
-      <c r="AX11" s="2">
+      <c r="BB11" s="2">
         <v>16860</v>
       </c>
-      <c r="AY11" s="2">
+      <c r="BC11" s="2">
         <v>16956</v>
       </c>
+      <c r="BD11" s="2">
+        <v>19498</v>
+      </c>
+      <c r="BE11" s="2">
+        <v>22505</v>
+      </c>
     </row>
-    <row r="12" spans="1:96" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:100" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <f>+E10-E11</f>
+        <f t="shared" ref="E12:M12" si="5">+E10-E11</f>
         <v>2622</v>
       </c>
       <c r="F12" s="6">
-        <f>+F10-F11</f>
+        <f t="shared" si="5"/>
         <v>893</v>
       </c>
       <c r="G12" s="10">
-        <f>+G10-G11</f>
+        <f t="shared" si="5"/>
         <v>-1206</v>
       </c>
       <c r="H12" s="10">
-        <f>+H10-H11</f>
+        <f t="shared" si="5"/>
         <v>-668</v>
       </c>
       <c r="I12" s="10">
-        <f>+I10-I11</f>
+        <f t="shared" si="5"/>
         <v>-435</v>
       </c>
       <c r="J12" s="10">
-        <f>+J10-J11</f>
+        <f t="shared" si="5"/>
         <v>-35</v>
       </c>
       <c r="K12" s="6">
-        <f>+K10-K11</f>
+        <f t="shared" si="5"/>
         <v>1079</v>
       </c>
       <c r="L12" s="6">
-        <f>+L10-L11</f>
+        <f t="shared" si="5"/>
         <v>1832</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="AD12" s="2">
+      <c r="M12" s="6">
+        <f t="shared" si="5"/>
+        <v>2737</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" ref="N12" si="6">+N10-N11</f>
+        <v>3348</v>
+      </c>
+      <c r="O12" s="2">
+        <f>+O10-O11</f>
+        <v>2963</v>
+      </c>
+      <c r="P12" s="2">
+        <f>+P10-P11</f>
+        <v>3508</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>+Q10-Q11</f>
+        <v>5054</v>
+      </c>
+      <c r="R12" s="2">
+        <f>+R10-R11</f>
+        <v>7646</v>
+      </c>
+      <c r="S12" s="2">
+        <f>+S10-S11</f>
+        <v>17755</v>
+      </c>
+      <c r="AH12" s="2">
         <v>-111</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AI12" s="2">
         <v>-21</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AJ12" s="2">
         <v>1314</v>
       </c>
-      <c r="AG12" s="2">
+      <c r="AK12" s="2">
         <v>1146</v>
       </c>
-      <c r="AH12" s="2">
+      <c r="AL12" s="2">
         <v>1200</v>
       </c>
-      <c r="AI12" s="2">
+      <c r="AM12" s="2">
         <v>1078</v>
       </c>
-      <c r="AJ12" s="2">
+      <c r="AN12" s="2">
         <v>-55</v>
       </c>
-      <c r="AK12" s="2">
+      <c r="AO12" s="2">
         <v>-440</v>
       </c>
-      <c r="AL12" s="2">
+      <c r="AP12" s="2">
         <v>2714</v>
       </c>
-      <c r="AM12" s="2">
+      <c r="AQ12" s="2">
         <v>1758</v>
       </c>
-      <c r="AN12" s="2">
+      <c r="AR12" s="2">
         <v>968</v>
       </c>
-      <c r="AO12" s="2">
+      <c r="AS12" s="2">
         <v>1847</v>
       </c>
-      <c r="AP12" s="2">
+      <c r="AT12" s="2">
         <v>5437</v>
       </c>
-      <c r="AQ12" s="2">
+      <c r="AU12" s="2">
         <v>5215</v>
       </c>
-      <c r="AR12" s="6">
+      <c r="AV12" s="6">
         <v>2505</v>
       </c>
-      <c r="AS12" s="2">
-        <f>+AS10-AS11</f>
+      <c r="AW12" s="2">
+        <f t="shared" ref="AW12:BC12" si="7">+AW10-AW11</f>
         <v>8436</v>
       </c>
-      <c r="AT12" s="2">
-        <f>+AT10-AT11</f>
+      <c r="AX12" s="2">
+        <f t="shared" si="7"/>
         <v>17891</v>
       </c>
-      <c r="AU12" s="2">
-        <f>+AU10-AU11</f>
+      <c r="AY12" s="2">
+        <f t="shared" si="7"/>
         <v>10702</v>
       </c>
-      <c r="AV12" s="2">
-        <f>+AV10-AV11</f>
+      <c r="AZ12" s="2">
+        <f t="shared" si="7"/>
         <v>6552</v>
       </c>
-      <c r="AW12" s="2">
-        <f>+AW10-AW11</f>
+      <c r="BA12" s="2">
+        <f t="shared" si="7"/>
         <v>10423</v>
       </c>
-      <c r="AX12" s="2">
-        <f>+AX10-AX11</f>
+      <c r="BB12" s="2">
+        <f t="shared" si="7"/>
         <v>13898</v>
       </c>
-      <c r="AY12" s="2">
-        <f>+AY10-AY11</f>
+      <c r="BC12" s="2">
+        <f t="shared" si="7"/>
         <v>-1416</v>
       </c>
+      <c r="BD12" s="2">
+        <v>5613</v>
+      </c>
+      <c r="BE12" s="2">
+        <f>+BE10-BE11</f>
+        <v>14873</v>
+      </c>
     </row>
-    <row r="13" spans="1:96" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:100" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -4609,90 +4741,90 @@
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
-      <c r="AR13" s="6"/>
+      <c r="AV13" s="6"/>
     </row>
-    <row r="14" spans="1:96" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="15" t="s">
+    <row r="14" spans="1:100" s="13" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14">
         <f>+J35</f>
         <v>1915</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="14">
         <f>+K35</f>
         <v>1924</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="14">
         <f>+L35</f>
         <v>1955</v>
       </c>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="AR14" s="16"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="AV14" s="14"/>
     </row>
-    <row r="15" spans="1:96" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="15" t="s">
+    <row r="15" spans="1:100" s="13" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B15" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16">
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14">
         <f>+J12+J14</f>
         <v>1880</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="14">
         <f>+K12+K14</f>
         <v>3003</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="14">
         <f>+L12+L14</f>
         <v>3787</v>
       </c>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="AR15" s="16"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="AV15" s="14"/>
     </row>
-    <row r="16" spans="1:96" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="15" t="s">
+    <row r="16" spans="1:100" s="13" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="17">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15">
         <f>+J15/J10</f>
         <v>0.3977994075327973</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="15">
         <f>+K15/K10</f>
         <v>0.515625</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="15">
         <f>+L15/L10</f>
         <v>0.55601233299075026</v>
       </c>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="AR16" s="16"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="AV16" s="14"/>
     </row>
-    <row r="17" spans="2:51" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:57" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -4705,9 +4837,9 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
-      <c r="AR17" s="6"/>
+      <c r="AV17" s="6"/>
     </row>
-    <row r="18" spans="2:51" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
@@ -4735,32 +4867,59 @@
       <c r="L18" s="6">
         <v>850</v>
       </c>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="AR18" s="6"/>
-      <c r="AS18" s="2">
+      <c r="M18" s="6">
+        <f>3430-L18-K18-J18</f>
+        <v>903</v>
+      </c>
+      <c r="N18" s="2">
+        <v>888</v>
+      </c>
+      <c r="O18" s="2">
+        <v>898</v>
+      </c>
+      <c r="P18" s="2">
+        <v>965</v>
+      </c>
+      <c r="Q18" s="2">
+        <f t="shared" ref="Q18:Q19" si="8">+BE18-P18-O18-N18</f>
+        <v>1047</v>
+      </c>
+      <c r="R18" s="2">
+        <v>1171</v>
+      </c>
+      <c r="S18" s="2">
+        <v>1250</v>
+      </c>
+      <c r="AV18" s="6"/>
+      <c r="AW18" s="2">
         <v>1824</v>
       </c>
-      <c r="AT18" s="2">
+      <c r="AX18" s="2">
         <v>2141</v>
       </c>
-      <c r="AU18" s="2">
+      <c r="AY18" s="2">
         <v>2441</v>
       </c>
-      <c r="AV18" s="2">
+      <c r="AZ18" s="2">
         <v>2600</v>
       </c>
-      <c r="AW18" s="2">
+      <c r="BA18" s="2">
         <v>2663</v>
       </c>
-      <c r="AX18" s="13">
+      <c r="BB18" s="2">
         <v>3116</v>
       </c>
-      <c r="AY18" s="2">
+      <c r="BC18" s="2">
         <v>3114</v>
       </c>
+      <c r="BD18" s="2">
+        <v>3430</v>
+      </c>
+      <c r="BE18" s="2">
+        <v>3798</v>
+      </c>
     </row>
-    <row r="19" spans="2:51" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
@@ -4788,172 +4947,267 @@
       <c r="L19" s="6">
         <v>291</v>
       </c>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="AR19" s="6"/>
-      <c r="AS19" s="2">
+      <c r="M19" s="6">
+        <f>1129-L19-K19-J19</f>
+        <v>295</v>
+      </c>
+      <c r="N19" s="2">
+        <v>288</v>
+      </c>
+      <c r="O19" s="2">
+        <v>285</v>
+      </c>
+      <c r="P19" s="2">
+        <v>318</v>
+      </c>
+      <c r="Q19" s="2">
+        <f t="shared" si="8"/>
+        <v>314</v>
+      </c>
+      <c r="R19" s="2">
+        <v>337</v>
+      </c>
+      <c r="S19" s="2">
+        <v>344</v>
+      </c>
+      <c r="AV19" s="6"/>
+      <c r="AW19" s="2">
         <v>743</v>
       </c>
-      <c r="AT19" s="2">
+      <c r="AX19" s="2">
         <v>813</v>
       </c>
-      <c r="AU19" s="2">
+      <c r="AY19" s="2">
         <v>836</v>
       </c>
-      <c r="AV19" s="2">
+      <c r="AZ19" s="2">
         <v>881</v>
       </c>
-      <c r="AW19" s="2">
+      <c r="BA19" s="2">
         <v>894</v>
       </c>
-      <c r="AX19" s="2">
+      <c r="BB19" s="2">
         <v>1066</v>
       </c>
-      <c r="AY19" s="2">
+      <c r="BC19" s="2">
         <v>920</v>
       </c>
+      <c r="BD19" s="2">
+        <v>1129</v>
+      </c>
+      <c r="BE19" s="2">
+        <v>1205</v>
+      </c>
     </row>
-    <row r="20" spans="2:51" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6">
-        <f t="shared" ref="E20:K20" si="4">+E18+E19</f>
+        <f t="shared" ref="E20:K20" si="9">+E18+E19</f>
         <v>1119</v>
       </c>
       <c r="F20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1100</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1019</v>
       </c>
       <c r="H20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>938</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1108</v>
       </c>
       <c r="K20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1112</v>
       </c>
       <c r="L20" s="6">
         <f>+L18+L19</f>
         <v>1141</v>
       </c>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="AR20" s="6"/>
-      <c r="AS20" s="2">
-        <f t="shared" ref="AS20:AX20" si="5">+AS19+AS18</f>
+      <c r="M20" s="6">
+        <f t="shared" ref="M20:S20" si="10">+M18+M19</f>
+        <v>1198</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" si="10"/>
+        <v>1176</v>
+      </c>
+      <c r="O20" s="6">
+        <f t="shared" si="10"/>
+        <v>1183</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" si="10"/>
+        <v>1283</v>
+      </c>
+      <c r="Q20" s="6">
+        <f t="shared" si="10"/>
+        <v>1361</v>
+      </c>
+      <c r="R20" s="6">
+        <f t="shared" si="10"/>
+        <v>1508</v>
+      </c>
+      <c r="S20" s="6">
+        <f t="shared" si="10"/>
+        <v>1594</v>
+      </c>
+      <c r="AV20" s="6"/>
+      <c r="AW20" s="2">
+        <f t="shared" ref="AW20:BB20" si="11">+AW19+AW18</f>
         <v>2567</v>
       </c>
-      <c r="AT20" s="2">
-        <f t="shared" si="5"/>
+      <c r="AX20" s="2">
+        <f t="shared" si="11"/>
         <v>2954</v>
       </c>
-      <c r="AU20" s="2">
-        <f t="shared" si="5"/>
+      <c r="AY20" s="2">
+        <f t="shared" si="11"/>
         <v>3277</v>
       </c>
-      <c r="AV20" s="2">
-        <f t="shared" si="5"/>
+      <c r="AZ20" s="2">
+        <f t="shared" si="11"/>
         <v>3481</v>
       </c>
-      <c r="AW20" s="2">
-        <f t="shared" si="5"/>
+      <c r="BA20" s="2">
+        <f t="shared" si="11"/>
         <v>3557</v>
       </c>
-      <c r="AX20" s="2">
-        <f t="shared" si="5"/>
+      <c r="BB20" s="2">
+        <f t="shared" si="11"/>
         <v>4182</v>
       </c>
-      <c r="AY20" s="2">
-        <f>+AY19+AY18</f>
+      <c r="BC20" s="2">
+        <f>+BC19+BC18</f>
         <v>4034</v>
       </c>
+      <c r="BD20" s="2">
+        <f t="shared" ref="BD20:BE20" si="12">+BD19+BD18</f>
+        <v>4559</v>
+      </c>
+      <c r="BE20" s="2">
+        <f t="shared" si="12"/>
+        <v>5003</v>
+      </c>
     </row>
-    <row r="21" spans="2:51" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6">
-        <f t="shared" ref="E21:K21" si="6">+E12-E20</f>
+        <f t="shared" ref="E21:K21" si="13">+E12-E20</f>
         <v>1503</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>-207</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>-2225</v>
       </c>
       <c r="H21" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>-668</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>-1373</v>
       </c>
       <c r="J21" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>-1143</v>
       </c>
       <c r="K21" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>-33</v>
       </c>
       <c r="L21" s="6">
         <f>+L12-L20</f>
         <v>691</v>
       </c>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="AR21" s="6"/>
-      <c r="AS21" s="2">
-        <f t="shared" ref="AS21:AX21" si="7">+AS12-AS20</f>
+      <c r="M21" s="6">
+        <f t="shared" ref="M21:S21" si="14">+M12-M20</f>
+        <v>1539</v>
+      </c>
+      <c r="N21" s="6">
+        <f t="shared" si="14"/>
+        <v>2172</v>
+      </c>
+      <c r="O21" s="6">
+        <f t="shared" si="14"/>
+        <v>1780</v>
+      </c>
+      <c r="P21" s="6">
+        <f t="shared" si="14"/>
+        <v>2225</v>
+      </c>
+      <c r="Q21" s="6">
+        <f t="shared" si="14"/>
+        <v>3693</v>
+      </c>
+      <c r="R21" s="6">
+        <f t="shared" si="14"/>
+        <v>6138</v>
+      </c>
+      <c r="S21" s="6">
+        <f t="shared" si="14"/>
+        <v>16161</v>
+      </c>
+      <c r="AV21" s="6"/>
+      <c r="AW21" s="2">
+        <f t="shared" ref="AW21:BB21" si="15">+AW12-AW20</f>
         <v>5869</v>
       </c>
-      <c r="AT21" s="2">
-        <f t="shared" si="7"/>
+      <c r="AX21" s="2">
+        <f t="shared" si="15"/>
         <v>14937</v>
       </c>
-      <c r="AU21" s="2">
-        <f t="shared" si="7"/>
+      <c r="AY21" s="2">
+        <f t="shared" si="15"/>
         <v>7425</v>
       </c>
-      <c r="AV21" s="2">
-        <f t="shared" si="7"/>
+      <c r="AZ21" s="2">
+        <f t="shared" si="15"/>
         <v>3071</v>
       </c>
-      <c r="AW21" s="2">
-        <f t="shared" si="7"/>
+      <c r="BA21" s="2">
+        <f t="shared" si="15"/>
         <v>6866</v>
       </c>
-      <c r="AX21" s="2">
-        <f t="shared" si="7"/>
+      <c r="BB21" s="2">
+        <f t="shared" si="15"/>
         <v>9716</v>
       </c>
-      <c r="AY21" s="2">
-        <f>+AY12-AY20</f>
+      <c r="BC21" s="2">
+        <f>+BC12-BC20</f>
         <v>-5450</v>
       </c>
+      <c r="BD21" s="2">
+        <f t="shared" ref="BD21:BE21" si="16">+BD12-BD20</f>
+        <v>1054</v>
+      </c>
+      <c r="BE21" s="2">
+        <f t="shared" si="16"/>
+        <v>9870</v>
+      </c>
     </row>
-    <row r="22" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:57" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
@@ -4981,61 +5235,97 @@
         <f>136-150+10</f>
         <v>-4</v>
       </c>
-      <c r="AS22">
+      <c r="M22" s="3">
+        <f>529-562</f>
+        <v>-33</v>
+      </c>
+      <c r="N22" s="3">
+        <f>107-118</f>
+        <v>-11</v>
+      </c>
+      <c r="O22">
+        <f>108-112</f>
+        <v>-4</v>
+      </c>
+      <c r="P22">
+        <f>135-123</f>
+        <v>12</v>
+      </c>
+      <c r="Q22" s="2">
+        <f>+BE22-P22-O22-N22</f>
+        <v>22</v>
+      </c>
+      <c r="R22">
+        <f>139-74</f>
+        <v>65</v>
+      </c>
+      <c r="S22">
+        <f>155-32</f>
+        <v>123</v>
+      </c>
+      <c r="AW22">
         <f>-1+41-601-112</f>
         <v>-673</v>
       </c>
-      <c r="AT22">
+      <c r="AX22">
         <f>57+120-342-465</f>
         <v>-630</v>
       </c>
-      <c r="AU22">
+      <c r="AY22">
         <f>-78+205-128-405</f>
         <v>-406</v>
       </c>
-      <c r="AV22">
+      <c r="AZ22">
         <f>-8+114-194+60</f>
         <v>-28</v>
       </c>
-      <c r="AW22">
+      <c r="BA22">
         <f>-95+37-183+81</f>
         <v>-160</v>
       </c>
-      <c r="AX22">
+      <c r="BB22">
         <f>34+96-189-38</f>
         <v>-97</v>
       </c>
-      <c r="AY22">
+      <c r="BC22">
         <f>-124+468-388+7</f>
         <v>-37</v>
       </c>
+      <c r="BD22">
+        <f>529-562</f>
+        <v>-33</v>
+      </c>
+      <c r="BE22">
+        <f>496-477</f>
+        <v>19</v>
+      </c>
     </row>
-    <row r="23" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:57" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="6">
-        <f t="shared" ref="E23:J23" si="8">+E21+E22</f>
+        <f t="shared" ref="E23:J23" si="17">+E21+E22</f>
         <v>1558</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>-251</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>-2201</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>-668</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>-1373</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>-1185</v>
       </c>
       <c r="K23" s="6">
@@ -5046,36 +5336,72 @@
         <f>+L21+L22</f>
         <v>687</v>
       </c>
-      <c r="AS23" s="2">
-        <f>+AS21+AS22</f>
+      <c r="M23" s="6">
+        <f t="shared" ref="M23:S23" si="18">+M21+M22</f>
+        <v>1506</v>
+      </c>
+      <c r="N23" s="6">
+        <f t="shared" si="18"/>
+        <v>2161</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" si="18"/>
+        <v>1776</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="18"/>
+        <v>2237</v>
+      </c>
+      <c r="Q23" s="6">
+        <f t="shared" si="18"/>
+        <v>3715</v>
+      </c>
+      <c r="R23" s="6">
+        <f t="shared" si="18"/>
+        <v>6203</v>
+      </c>
+      <c r="S23" s="6">
+        <f t="shared" si="18"/>
+        <v>16284</v>
+      </c>
+      <c r="AW23" s="2">
+        <f t="shared" ref="AW23:BC23" si="19">+AW21+AW22</f>
         <v>5196</v>
       </c>
-      <c r="AT23" s="2">
-        <f>+AT21+AT22</f>
+      <c r="AX23" s="2">
+        <f t="shared" si="19"/>
         <v>14307</v>
       </c>
-      <c r="AU23" s="2">
-        <f>+AU21+AU22</f>
+      <c r="AY23" s="2">
+        <f t="shared" si="19"/>
         <v>7019</v>
       </c>
-      <c r="AV23" s="2">
-        <f>+AV21+AV22</f>
+      <c r="AZ23" s="2">
+        <f t="shared" si="19"/>
         <v>3043</v>
       </c>
-      <c r="AW23" s="2">
-        <f>+AW21+AW22</f>
+      <c r="BA23" s="2">
+        <f t="shared" si="19"/>
         <v>6706</v>
       </c>
-      <c r="AX23" s="2">
-        <f>+AX21+AX22</f>
+      <c r="BB23" s="2">
+        <f t="shared" si="19"/>
         <v>9619</v>
       </c>
-      <c r="AY23" s="2">
-        <f>+AY21+AY22</f>
+      <c r="BC23" s="2">
+        <f t="shared" si="19"/>
         <v>-5487</v>
       </c>
+      <c r="BD23" s="2">
+        <f t="shared" ref="BD23" si="20">+BD21+BD22</f>
+        <v>1021</v>
+      </c>
+      <c r="BE23" s="2">
+        <f t="shared" ref="BE23" si="21">+BE21+BE22</f>
+        <v>9889</v>
+      </c>
     </row>
-    <row r="24" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:57" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
@@ -5098,61 +5424,89 @@
         <f>377+6</f>
         <v>383</v>
       </c>
-      <c r="AS24">
+      <c r="M24" s="3">
+        <v>451</v>
+      </c>
+      <c r="N24" s="3">
+        <v>283</v>
+      </c>
+      <c r="O24" s="2">
+        <v>177</v>
+      </c>
+      <c r="P24" s="2">
+        <v>235</v>
+      </c>
+      <c r="Q24" s="2">
+        <f>+BE24-P24-O24-N24</f>
+        <v>429</v>
+      </c>
+      <c r="R24" s="2">
+        <v>829</v>
+      </c>
+      <c r="S24" s="2">
+        <v>2371</v>
+      </c>
+      <c r="AW24">
         <f>114-8</f>
         <v>106</v>
       </c>
-      <c r="AT24">
+      <c r="AX24">
         <f>168+1</f>
         <v>169</v>
       </c>
-      <c r="AU24">
+      <c r="AY24">
         <f>693-3</f>
         <v>690</v>
       </c>
-      <c r="AV24">
+      <c r="AZ24">
         <f>280-7</f>
         <v>273</v>
       </c>
-      <c r="AW24">
+      <c r="BA24">
         <f>394-37</f>
         <v>357</v>
       </c>
-      <c r="AX24">
+      <c r="BB24">
         <f>888-4</f>
         <v>884</v>
       </c>
-      <c r="AY24">
+      <c r="BC24">
         <f>177-2</f>
         <v>175</v>
       </c>
+      <c r="BD24">
+        <v>451</v>
+      </c>
+      <c r="BE24" s="2">
+        <v>1124</v>
+      </c>
     </row>
-    <row r="25" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:57" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" ref="E25:J25" si="9">+E23-E24</f>
+        <f t="shared" ref="E25:J25" si="22">+E23-E24</f>
         <v>1497</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-270</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-2201</v>
       </c>
       <c r="H25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-668</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-1373</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-1264</v>
       </c>
       <c r="K25" s="6">
@@ -5163,101 +5517,173 @@
         <f>+L23-L24</f>
         <v>304</v>
       </c>
-      <c r="AS25" s="2">
-        <f>+AS23-AS24</f>
+      <c r="M25" s="6">
+        <f t="shared" ref="M25:S25" si="23">+M23-M24</f>
+        <v>1055</v>
+      </c>
+      <c r="N25" s="6">
+        <f t="shared" si="23"/>
+        <v>1878</v>
+      </c>
+      <c r="O25" s="6">
+        <f t="shared" si="23"/>
+        <v>1599</v>
+      </c>
+      <c r="P25" s="6">
+        <f t="shared" si="23"/>
+        <v>2002</v>
+      </c>
+      <c r="Q25" s="6">
+        <f t="shared" si="23"/>
+        <v>3286</v>
+      </c>
+      <c r="R25" s="6">
+        <f t="shared" si="23"/>
+        <v>5374</v>
+      </c>
+      <c r="S25" s="6">
+        <f t="shared" si="23"/>
+        <v>13913</v>
+      </c>
+      <c r="AW25" s="2">
+        <f t="shared" ref="AW25:BC25" si="24">+AW23-AW24</f>
         <v>5090</v>
       </c>
-      <c r="AT25" s="2">
-        <f>+AT23-AT24</f>
+      <c r="AX25" s="2">
+        <f t="shared" si="24"/>
         <v>14138</v>
       </c>
-      <c r="AU25" s="2">
-        <f>+AU23-AU24</f>
+      <c r="AY25" s="2">
+        <f t="shared" si="24"/>
         <v>6329</v>
       </c>
-      <c r="AV25" s="2">
-        <f>+AV23-AV24</f>
+      <c r="AZ25" s="2">
+        <f t="shared" si="24"/>
         <v>2770</v>
       </c>
-      <c r="AW25" s="2">
-        <f>+AW23-AW24</f>
+      <c r="BA25" s="2">
+        <f t="shared" si="24"/>
         <v>6349</v>
       </c>
-      <c r="AX25" s="2">
-        <f>+AX23-AX24</f>
+      <c r="BB25" s="2">
+        <f t="shared" si="24"/>
         <v>8735</v>
       </c>
-      <c r="AY25" s="2">
-        <f>+AY23-AY24</f>
+      <c r="BC25" s="2">
+        <f t="shared" si="24"/>
         <v>-5662</v>
       </c>
+      <c r="BD25" s="2">
+        <f t="shared" ref="BD25" si="25">+BD23-BD24</f>
+        <v>570</v>
+      </c>
+      <c r="BE25" s="2">
+        <f t="shared" ref="BE25" si="26">+BE23-BE24</f>
+        <v>8765</v>
+      </c>
     </row>
-    <row r="26" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:57" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E26" s="8">
-        <f>+E25/E27</f>
+        <f t="shared" ref="E26:L26" si="27">+E25/E27</f>
         <v>1.3535262206148282</v>
       </c>
       <c r="F26" s="8">
-        <f>+F25/F27</f>
+        <f t="shared" si="27"/>
         <v>-0.24657534246575341</v>
       </c>
       <c r="G26" s="8">
-        <f>+G25/G27</f>
+        <f t="shared" si="27"/>
         <v>-2.0174152153987168</v>
       </c>
       <c r="H26" s="8" t="e">
-        <f>+H25/H27</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="8">
-        <f>+I25/I27</f>
+        <f t="shared" si="27"/>
         <v>-1.2538812785388127</v>
       </c>
       <c r="J26" s="8">
-        <f>+J25/J27</f>
+        <f t="shared" si="27"/>
         <v>-1.1490909090909092</v>
       </c>
       <c r="K26" s="8">
-        <f>+K25/K27</f>
+        <f t="shared" si="27"/>
         <v>-0.6077199281867145</v>
       </c>
       <c r="L26" s="8">
-        <f>+L25/L27</f>
+        <f t="shared" si="27"/>
         <v>0.27070347284060553</v>
       </c>
-      <c r="AS26" s="1">
-        <f>+AS25/AS27</f>
+      <c r="M26" s="8">
+        <f t="shared" ref="M26" si="28">+M25/M27</f>
+        <v>0.94364937388193204</v>
+      </c>
+      <c r="N26" s="8">
+        <f t="shared" ref="N26" si="29">+N25/N27</f>
+        <v>1.6737967914438503</v>
+      </c>
+      <c r="O26" s="8">
+        <f t="shared" ref="O26" si="30">+O25/O27</f>
+        <v>1.4238646482635797</v>
+      </c>
+      <c r="P26" s="8">
+        <f t="shared" ref="P26" si="31">+P25/P27</f>
+        <v>1.7795555555555556</v>
+      </c>
+      <c r="Q26" s="8">
+        <f t="shared" ref="Q26" si="32">+Q25/Q27</f>
+        <v>2.9208888888888889</v>
+      </c>
+      <c r="R26" s="8">
+        <f t="shared" ref="R26" si="33">+R25/R27</f>
+        <v>4.72231985940246</v>
+      </c>
+      <c r="S26" s="8">
+        <f t="shared" ref="S26" si="34">+S25/S27</f>
+        <v>12.183012259194395</v>
+      </c>
+      <c r="AW26" s="1">
+        <f t="shared" ref="AW26:BE26" si="35">+AW25/AW27</f>
         <v>4.4107452339688038</v>
       </c>
-      <c r="AT26" s="1">
-        <f>+AT25/AT27</f>
+      <c r="AX26" s="1">
+        <f t="shared" si="35"/>
         <v>11.503661513425548</v>
       </c>
-      <c r="AU26" s="1">
-        <f>+AU25/AU27</f>
+      <c r="AY26" s="1">
+        <f t="shared" si="35"/>
         <v>5.5371828521434825</v>
       </c>
-      <c r="AV26" s="1">
-        <f>+AV25/AV27</f>
+      <c r="AZ26" s="1">
+        <f t="shared" si="35"/>
         <v>2.4491600353669321</v>
       </c>
-      <c r="AW26" s="1">
-        <f>+AW25/AW27</f>
+      <c r="BA26" s="1">
+        <f t="shared" si="35"/>
         <v>5.5644171779141107</v>
       </c>
-      <c r="AX26" s="1">
-        <f>+AX25/AX27</f>
+      <c r="BB26" s="1">
+        <f t="shared" si="35"/>
         <v>7.785204991087344</v>
       </c>
-      <c r="AY26" s="1">
-        <f>+AY25/AY27</f>
+      <c r="BC26" s="1">
+        <f t="shared" si="35"/>
         <v>-5.1802378774016464</v>
       </c>
+      <c r="BD26" s="1">
+        <f t="shared" si="35"/>
+        <v>0.50983899821109124</v>
+      </c>
+      <c r="BE26" s="1">
+        <f t="shared" si="35"/>
+        <v>7.7911111111111113</v>
+      </c>
     </row>
-    <row r="27" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:57" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>1</v>
       </c>
@@ -5282,38 +5708,66 @@
       <c r="L27" s="6">
         <v>1123</v>
       </c>
-      <c r="AS27" s="2">
+      <c r="M27" s="6">
+        <v>1118</v>
+      </c>
+      <c r="N27" s="6">
+        <v>1122</v>
+      </c>
+      <c r="O27" s="6">
+        <v>1123</v>
+      </c>
+      <c r="P27" s="2">
+        <v>1125</v>
+      </c>
+      <c r="Q27" s="2">
+        <f>BE27</f>
+        <v>1125</v>
+      </c>
+      <c r="R27" s="2">
+        <v>1138</v>
+      </c>
+      <c r="S27" s="6">
+        <v>1142</v>
+      </c>
+      <c r="AW27" s="2">
         <v>1154</v>
       </c>
-      <c r="AT27" s="2">
+      <c r="AX27" s="2">
         <v>1229</v>
       </c>
-      <c r="AU27" s="2">
+      <c r="AY27" s="2">
         <v>1143</v>
       </c>
-      <c r="AV27" s="2">
+      <c r="AZ27" s="2">
         <v>1131</v>
       </c>
-      <c r="AW27" s="2">
+      <c r="BA27" s="2">
         <v>1141</v>
       </c>
-      <c r="AX27" s="2">
+      <c r="BB27" s="2">
         <v>1122</v>
       </c>
-      <c r="AY27" s="2">
+      <c r="BC27" s="2">
         <v>1093</v>
       </c>
+      <c r="BD27" s="2">
+        <v>1118</v>
+      </c>
+      <c r="BE27" s="2">
+        <v>1125</v>
+      </c>
     </row>
-    <row r="30" spans="2:51" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:57" s="18" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
       <c r="I30" s="12">
         <f>+I10/E10-1</f>
         <v>-0.39635706758994427</v>
@@ -5332,220 +5786,271 @@
       </c>
       <c r="M30" s="12">
         <f>+M10/I10-1</f>
-        <v>0.89526184538653375</v>
-      </c>
-      <c r="N30" s="19"/>
-      <c r="AE30" s="21">
-        <f t="shared" ref="AE30:AL30" si="10">+AE10/AD10-1</f>
+        <v>0.93266832917705744</v>
+      </c>
+      <c r="N30" s="12">
+        <f t="shared" ref="N30:S30" si="36">+N10/J10-1</f>
+        <v>0.84278459585272958</v>
+      </c>
+      <c r="O30" s="12">
+        <f t="shared" si="36"/>
+        <v>0.38272664835164827</v>
+      </c>
+      <c r="P30" s="12">
+        <f t="shared" si="36"/>
+        <v>0.36558508295404502</v>
+      </c>
+      <c r="Q30" s="12">
+        <f t="shared" si="36"/>
+        <v>0.45999999999999996</v>
+      </c>
+      <c r="R30" s="12">
+        <f t="shared" si="36"/>
+        <v>0.56654036054656109</v>
+      </c>
+      <c r="S30" s="12">
+        <f t="shared" si="36"/>
+        <v>1.9628709797590962</v>
+      </c>
+      <c r="AI30" s="19">
+        <f t="shared" ref="AI30:AO30" si="37">+AI10/AH10-1</f>
         <v>0.19389725762842791</v>
       </c>
-      <c r="AF30" s="21">
-        <f t="shared" si="10"/>
+      <c r="AJ30" s="19">
+        <f t="shared" si="37"/>
         <v>0.42478162406988029</v>
       </c>
-      <c r="AG30" s="21">
-        <f t="shared" si="10"/>
+      <c r="AK30" s="19">
+        <f t="shared" si="37"/>
         <v>0.10808356039963662</v>
       </c>
-      <c r="AH30" s="21">
-        <f t="shared" si="10"/>
+      <c r="AL30" s="19">
+        <f t="shared" si="37"/>
         <v>8.0327868852458906E-2</v>
       </c>
-      <c r="AI30" s="21">
-        <f t="shared" si="10"/>
+      <c r="AM30" s="19">
+        <f t="shared" si="37"/>
         <v>7.8907435508345891E-2</v>
       </c>
-      <c r="AJ30" s="21">
-        <f t="shared" si="10"/>
+      <c r="AN30" s="19">
+        <f t="shared" si="37"/>
         <v>2.6898734177215111E-2</v>
       </c>
-      <c r="AK30" s="21">
-        <f t="shared" si="10"/>
+      <c r="AO30" s="19">
+        <f t="shared" si="37"/>
         <v>-0.17770929635336419</v>
       </c>
-      <c r="AL30" s="21">
-        <f t="shared" ref="AL30:AT30" si="11">+AL10/AK10-1</f>
+      <c r="AP30" s="19">
+        <f t="shared" ref="AP30:AW30" si="38">+AP10/AO10-1</f>
         <v>0.76597959608577981</v>
       </c>
-      <c r="AM30" s="21">
-        <f t="shared" si="11"/>
+      <c r="AQ30" s="19">
+        <f t="shared" si="38"/>
         <v>3.6076397076161282E-2</v>
       </c>
-      <c r="AN30" s="21">
-        <f t="shared" si="11"/>
+      <c r="AR30" s="19">
+        <f t="shared" si="38"/>
         <v>-6.3040509786071897E-2</v>
       </c>
-      <c r="AO30" s="21">
-        <f t="shared" si="11"/>
+      <c r="AS30" s="19">
+        <f t="shared" si="38"/>
         <v>0.10189458343453972</v>
       </c>
-      <c r="AP30" s="21">
-        <f t="shared" si="11"/>
+      <c r="AT30" s="19">
+        <f t="shared" si="38"/>
         <v>0.80293177559792794</v>
       </c>
-      <c r="AQ30" s="21">
-        <f t="shared" si="11"/>
+      <c r="AU30" s="19">
+        <f t="shared" si="38"/>
         <v>-1.0147939845946974E-2</v>
       </c>
-      <c r="AR30" s="21">
-        <f t="shared" si="11"/>
+      <c r="AV30" s="19">
+        <f t="shared" si="38"/>
         <v>-0.23425148221343872</v>
       </c>
-      <c r="AS30" s="21">
-        <f t="shared" si="11"/>
+      <c r="AW30" s="19">
+        <f t="shared" si="38"/>
         <v>0.63900314541495273</v>
       </c>
-      <c r="AT30" s="21">
-        <f>+AT10/AS10-1</f>
+      <c r="AX30" s="19">
+        <f t="shared" ref="AX30:BC30" si="39">+AX10/AW10-1</f>
         <v>0.49547288652691668</v>
       </c>
-      <c r="AU30" s="21">
-        <f>+AU10/AT10-1</f>
+      <c r="AY30" s="19">
+        <f t="shared" si="39"/>
         <v>-0.22983778092198348</v>
       </c>
-      <c r="AV30" s="21">
-        <f>+AV10/AU10-1</f>
+      <c r="AZ30" s="19">
+        <f t="shared" si="39"/>
         <v>-8.4209177134068169E-2</v>
       </c>
-      <c r="AW30" s="21">
-        <f>+AW10/AV10-1</f>
+      <c r="BA30" s="19">
+        <f t="shared" si="39"/>
         <v>0.29251224632610207</v>
       </c>
-      <c r="AX30" s="21">
-        <f>+AX10/AW10-1</f>
+      <c r="BB30" s="19">
+        <f t="shared" si="39"/>
         <v>0.11019671539433307</v>
       </c>
-      <c r="AY30" s="21">
-        <f>+AY10/AX10-1</f>
+      <c r="BC30" s="19">
+        <f t="shared" si="39"/>
         <v>-0.4947655894401457</v>
       </c>
     </row>
-    <row r="31" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:57" ht="13" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E31" s="7">
-        <f>+E12/E10</f>
+        <f t="shared" ref="E31:S31" si="40">+E12/E10</f>
         <v>0.39470118922173719</v>
       </c>
       <c r="F31" s="7">
-        <f>+F12/F10</f>
+        <f t="shared" si="40"/>
         <v>0.21860465116279071</v>
       </c>
       <c r="G31" s="12">
-        <f>+G12/G10</f>
+        <f t="shared" si="40"/>
         <v>-0.32656376929325753</v>
       </c>
       <c r="H31" s="12">
-        <f>+H12/H10</f>
+        <f t="shared" si="40"/>
         <v>-0.17803837953091683</v>
       </c>
       <c r="I31" s="12">
-        <f>+I12/I10</f>
+        <f t="shared" si="40"/>
         <v>-0.10847880299251871</v>
       </c>
       <c r="J31" s="12">
-        <f>+J12/J10</f>
+        <f t="shared" si="40"/>
         <v>-7.4058400338552688E-3</v>
       </c>
       <c r="K31" s="7">
-        <f>+K12/K10</f>
+        <f t="shared" si="40"/>
         <v>0.18526785714285715</v>
       </c>
       <c r="L31" s="7">
-        <f>+L12/L10</f>
+        <f t="shared" si="40"/>
         <v>0.26897665541036558</v>
       </c>
-      <c r="AD31" s="7">
-        <f t="shared" ref="AD31:AK31" si="12">+AD12/AD10</f>
+      <c r="M31" s="7">
+        <f t="shared" si="40"/>
+        <v>0.35316129032258065</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="40"/>
+        <v>0.38442990010334138</v>
+      </c>
+      <c r="O31" s="7">
+        <f t="shared" si="40"/>
+        <v>0.36793741462808893</v>
+      </c>
+      <c r="P31" s="7">
+        <f t="shared" si="40"/>
+        <v>0.37716374583378132</v>
+      </c>
+      <c r="Q31" s="7">
+        <f t="shared" si="40"/>
+        <v>0.44666372072470173</v>
+      </c>
+      <c r="R31" s="7">
+        <f t="shared" si="40"/>
+        <v>0.56043392215788312</v>
+      </c>
+      <c r="S31" s="7">
+        <f t="shared" si="40"/>
+        <v>0.74413243922883487</v>
+      </c>
+      <c r="AH31" s="7">
+        <f t="shared" ref="AH31:AN31" si="41">+AH12/AH10</f>
         <v>-4.287369640787949E-2</v>
       </c>
-      <c r="AE31" s="7">
-        <f t="shared" si="12"/>
+      <c r="AI31" s="7">
+        <f t="shared" si="41"/>
         <v>-6.7939178259462957E-3</v>
       </c>
-      <c r="AF31" s="7">
-        <f t="shared" si="12"/>
+      <c r="AJ31" s="7">
+        <f t="shared" si="41"/>
         <v>0.29836512261580383</v>
       </c>
-      <c r="AG31" s="7">
-        <f t="shared" si="12"/>
+      <c r="AK31" s="7">
+        <f t="shared" si="41"/>
         <v>0.23483606557377049</v>
       </c>
-      <c r="AH31" s="7">
-        <f t="shared" si="12"/>
+      <c r="AL31" s="7">
+        <f t="shared" si="41"/>
         <v>0.22761760242792109</v>
       </c>
-      <c r="AI31" s="7">
-        <f t="shared" si="12"/>
+      <c r="AM31" s="7">
+        <f t="shared" si="41"/>
         <v>0.18952180028129395</v>
       </c>
-      <c r="AJ31" s="7">
-        <f t="shared" si="12"/>
+      <c r="AN31" s="7">
+        <f t="shared" si="41"/>
         <v>-9.4161958568738224E-3</v>
       </c>
-      <c r="AK31" s="7">
-        <f t="shared" ref="AK31:AS31" si="13">+AK12/AK10</f>
+      <c r="AO31" s="7">
+        <f t="shared" ref="AO31:AV31" si="42">+AO12/AO10</f>
         <v>-9.1609410784926085E-2</v>
       </c>
-      <c r="AL31" s="7">
-        <f t="shared" si="13"/>
+      <c r="AP31" s="7">
+        <f t="shared" si="42"/>
         <v>0.31997170478660691</v>
       </c>
-      <c r="AM31" s="7">
-        <f t="shared" si="13"/>
+      <c r="AQ31" s="7">
+        <f t="shared" si="42"/>
         <v>0.20004551661356396</v>
       </c>
-      <c r="AN31" s="7">
-        <f t="shared" si="13"/>
+      <c r="AR31" s="7">
+        <f t="shared" si="42"/>
         <v>0.11756133106631042</v>
       </c>
-      <c r="AO31" s="7">
-        <f t="shared" si="13"/>
+      <c r="AS31" s="7">
+        <f t="shared" si="42"/>
         <v>0.2035710349388295</v>
       </c>
-      <c r="AP31" s="7">
-        <f t="shared" si="13"/>
+      <c r="AT31" s="7">
+        <f t="shared" si="42"/>
         <v>0.33237559603863553</v>
       </c>
-      <c r="AQ31" s="7">
-        <f t="shared" si="13"/>
+      <c r="AU31" s="7">
+        <f t="shared" si="42"/>
         <v>0.32207262845849804</v>
       </c>
-      <c r="AR31" s="7">
-        <f t="shared" si="13"/>
+      <c r="AV31" s="7">
+        <f t="shared" si="42"/>
         <v>0.20203242196951368</v>
       </c>
-      <c r="AS31" s="7">
-        <f t="shared" ref="AS31:AU31" si="14">+AS12/AS10</f>
+      <c r="AW31" s="7">
+        <f t="shared" ref="AW31:AY31" si="43">+AW12/AW10</f>
         <v>0.41511662237968705</v>
       </c>
-      <c r="AT31" s="7">
-        <f t="shared" si="14"/>
+      <c r="AX31" s="7">
+        <f t="shared" si="43"/>
         <v>0.588694021256293</v>
       </c>
-      <c r="AU31" s="7">
-        <f t="shared" si="14"/>
+      <c r="AY31" s="7">
+        <f t="shared" si="43"/>
         <v>0.45723318807143465</v>
       </c>
-      <c r="AV31" s="7">
-        <f t="shared" ref="AV31:AY31" si="15">+AV12/AV10</f>
+      <c r="AZ31" s="7">
+        <f t="shared" ref="AZ31:BC31" si="44">+AZ12/AZ10</f>
         <v>0.30566829951014696</v>
       </c>
-      <c r="AW31" s="7">
-        <f t="shared" si="15"/>
+      <c r="BA31" s="7">
+        <f t="shared" si="44"/>
         <v>0.37621367984118392</v>
       </c>
-      <c r="AX31" s="7">
-        <f t="shared" si="15"/>
+      <c r="BB31" s="7">
+        <f t="shared" si="44"/>
         <v>0.45184992522270628</v>
       </c>
-      <c r="AY31" s="7">
-        <f t="shared" si="15"/>
+      <c r="BC31" s="7">
+        <f t="shared" si="44"/>
         <v>-9.1119691119691121E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:55" ht="13" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>35</v>
       </c>
@@ -5562,7 +6067,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="34" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>36</v>
       </c>
@@ -5578,7 +6083,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>37</v>
       </c>
@@ -5594,7 +6099,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="36" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>38</v>
       </c>
@@ -5610,7 +6115,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>39</v>
       </c>
@@ -5627,7 +6132,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="38" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>40</v>
       </c>
@@ -5643,74 +6148,70 @@
         <f>SUM(L34:L37)</f>
         <v>2482</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AJ38" s="2">
         <v>1159</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AK38" s="2">
         <v>1237</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AL38" s="2">
         <v>2019</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AM38" s="2">
         <v>937</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AN38" s="2">
         <v>1018</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AO38" s="2">
         <v>1206</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AP38" s="2">
         <v>3096</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AQ38" s="2">
         <v>2484</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AR38" s="2">
         <v>2114</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AS38" s="2">
         <v>1811</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AT38" s="2">
         <v>5699</v>
       </c>
-      <c r="AQ38" s="2">
+      <c r="AU38" s="2">
         <v>5208</v>
       </c>
-      <c r="AR38" s="6">
+      <c r="AV38" s="6">
         <v>3168</v>
       </c>
-      <c r="AS38" s="2">
+      <c r="AW38" s="2">
         <v>8153</v>
       </c>
-      <c r="AT38" s="2">
+      <c r="AX38" s="2">
         <v>17400</v>
       </c>
-      <c r="AU38" s="2">
+      <c r="AY38" s="2">
         <v>13189</v>
       </c>
-      <c r="AV38" s="2">
+      <c r="AZ38" s="2">
         <v>8306</v>
       </c>
-      <c r="AW38" s="2">
+      <c r="BA38" s="2">
         <v>12468</v>
       </c>
-      <c r="AX38" s="2">
+      <c r="BB38" s="2">
         <v>15181</v>
       </c>
-      <c r="AY38" s="2">
+      <c r="BC38" s="2">
         <v>1559</v>
       </c>
     </row>
-    <row r="39" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:55" x14ac:dyDescent="0.25">
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
-      <c r="AF39" s="2"/>
-      <c r="AG39" s="2"/>
-      <c r="AH39" s="2"/>
-      <c r="AI39" s="2"/>
       <c r="AJ39" s="2"/>
       <c r="AK39" s="2"/>
       <c r="AL39" s="2"/>
@@ -5719,16 +6220,20 @@
       <c r="AO39" s="2"/>
       <c r="AP39" s="2"/>
       <c r="AQ39" s="2"/>
-      <c r="AR39" s="6"/>
+      <c r="AR39" s="2"/>
       <c r="AS39" s="2"/>
       <c r="AT39" s="2"/>
       <c r="AU39" s="2"/>
-      <c r="AV39" s="2"/>
+      <c r="AV39" s="6"/>
       <c r="AW39" s="2"/>
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
+      <c r="AZ39" s="2"/>
+      <c r="BA39" s="2"/>
+      <c r="BB39" s="2"/>
+      <c r="BC39" s="2"/>
     </row>
-    <row r="40" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>52</v>
       </c>
@@ -5743,68 +6248,68 @@
         <f>-5266-K40-J40</f>
         <v>-2086</v>
       </c>
-      <c r="AF40" s="2">
+      <c r="AJ40" s="2">
         <v>1799</v>
       </c>
-      <c r="AG40" s="2">
+      <c r="AK40" s="2">
         <v>1849</v>
       </c>
-      <c r="AH40" s="2">
+      <c r="AL40" s="2">
         <v>-1365</v>
       </c>
-      <c r="AI40" s="2">
+      <c r="AM40" s="2">
         <v>-3603</v>
       </c>
-      <c r="AJ40" s="2">
+      <c r="AN40" s="2">
         <v>-2529</v>
       </c>
-      <c r="AK40" s="2">
+      <c r="AO40" s="2">
         <v>-488</v>
       </c>
-      <c r="AL40" s="2">
+      <c r="AP40" s="2">
         <v>-616</v>
       </c>
-      <c r="AM40" s="2">
+      <c r="AQ40" s="2">
         <v>-2550</v>
       </c>
-      <c r="AN40" s="2">
+      <c r="AR40" s="2">
         <v>-1699</v>
       </c>
-      <c r="AO40" s="2">
+      <c r="AS40" s="2">
         <v>-1442</v>
       </c>
-      <c r="AP40" s="2">
+      <c r="AT40" s="2">
         <v>-3107</v>
       </c>
-      <c r="AQ40" s="2">
+      <c r="AU40" s="2">
         <v>-4021</v>
       </c>
-      <c r="AR40" s="6">
+      <c r="AV40" s="6">
         <v>-5817</v>
       </c>
-      <c r="AS40" s="2">
+      <c r="AW40" s="2">
         <v>-4734</v>
       </c>
-      <c r="AT40" s="2">
+      <c r="AX40" s="2">
         <v>-8879</v>
       </c>
-      <c r="AU40" s="2">
+      <c r="AY40" s="2">
         <v>-9780</v>
       </c>
-      <c r="AV40" s="2">
+      <c r="AZ40" s="2">
         <v>-8223</v>
       </c>
-      <c r="AW40" s="2">
+      <c r="BA40" s="2">
         <v>-10030</v>
       </c>
-      <c r="AX40" s="2">
+      <c r="BB40" s="2">
         <v>-12067</v>
       </c>
-      <c r="AY40" s="2">
+      <c r="BC40" s="2">
         <v>-7676</v>
       </c>
     </row>
-    <row r="41" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>43</v>
       </c>
@@ -5821,7 +6326,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>44</v>
       </c>
@@ -5837,7 +6342,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>45</v>
       </c>
@@ -5853,7 +6358,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="44" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>42</v>
       </c>
@@ -5870,11 +6375,11 @@
         <v>-2002</v>
       </c>
     </row>
-    <row r="45" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:55" x14ac:dyDescent="0.25">
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>47</v>
       </c>
@@ -5890,7 +6395,7 @@
         <v>-128</v>
       </c>
     </row>
-    <row r="47" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>46</v>
       </c>
@@ -5906,7 +6411,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="48" spans="2:51" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>4</v>
       </c>
@@ -5922,7 +6427,7 @@
         <v>-715</v>
       </c>
     </row>
-    <row r="49" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>45</v>
       </c>
@@ -5938,7 +6443,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="50" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>50</v>
       </c>
@@ -5955,7 +6460,7 @@
         <v>-910</v>
       </c>
     </row>
-    <row r="51" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>49</v>
       </c>
@@ -5971,7 +6476,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="52" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>48</v>
       </c>
@@ -5988,7 +6493,7 @@
         <v>-437</v>
       </c>
     </row>
-    <row r="54" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:56" ht="13" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>51</v>
       </c>
@@ -6004,732 +6509,720 @@
         <f>+L38+L40</f>
         <v>396</v>
       </c>
-      <c r="AF54" s="9">
-        <f>+AF38+AF40</f>
+      <c r="AJ54" s="9">
+        <f>+AJ38+AJ40</f>
         <v>2958</v>
       </c>
-      <c r="AG54" s="9">
-        <f t="shared" ref="AF54:AM54" si="16">+AG38+AG40</f>
+      <c r="AK54" s="9">
+        <f t="shared" ref="AK54:AP54" si="45">+AK38+AK40</f>
         <v>3086</v>
       </c>
-      <c r="AH54" s="9">
-        <f t="shared" si="16"/>
+      <c r="AL54" s="9">
+        <f t="shared" si="45"/>
         <v>654</v>
       </c>
-      <c r="AI54" s="9">
-        <f t="shared" si="16"/>
+      <c r="AM54" s="9">
+        <f t="shared" si="45"/>
         <v>-2666</v>
       </c>
-      <c r="AJ54" s="9">
-        <f t="shared" si="16"/>
+      <c r="AN54" s="9">
+        <f t="shared" si="45"/>
         <v>-1511</v>
       </c>
-      <c r="AK54" s="9">
-        <f t="shared" si="16"/>
+      <c r="AO54" s="9">
+        <f t="shared" si="45"/>
         <v>718</v>
       </c>
-      <c r="AL54" s="9">
-        <f t="shared" si="16"/>
+      <c r="AP54" s="9">
+        <f t="shared" si="45"/>
         <v>2480</v>
       </c>
-      <c r="AM54" s="9">
-        <f t="shared" ref="AM54:AW54" si="17">+AM38+AM40</f>
+      <c r="AQ54" s="9">
+        <f t="shared" ref="AQ54:AZ54" si="46">+AQ38+AQ40</f>
         <v>-66</v>
       </c>
-      <c r="AN54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AR54" s="9">
+        <f t="shared" si="46"/>
         <v>415</v>
       </c>
-      <c r="AO54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AS54" s="9">
+        <f t="shared" si="46"/>
         <v>369</v>
       </c>
-      <c r="AP54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AT54" s="9">
+        <f t="shared" si="46"/>
         <v>2592</v>
       </c>
-      <c r="AQ54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AU54" s="9">
+        <f t="shared" si="46"/>
         <v>1187</v>
       </c>
-      <c r="AR54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AV54" s="9">
+        <f t="shared" si="46"/>
         <v>-2649</v>
       </c>
-      <c r="AS54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AW54" s="9">
+        <f t="shared" si="46"/>
         <v>3419</v>
       </c>
-      <c r="AT54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AX54" s="9">
+        <f t="shared" si="46"/>
         <v>8521</v>
       </c>
-      <c r="AU54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AY54" s="9">
+        <f t="shared" si="46"/>
         <v>3409</v>
       </c>
-      <c r="AV54" s="9">
-        <f t="shared" si="17"/>
+      <c r="AZ54" s="9">
+        <f t="shared" si="46"/>
         <v>83</v>
       </c>
-      <c r="AW54" s="9">
-        <f>+AW38+AW40</f>
+      <c r="BA54" s="9">
+        <f>+BA38+BA40</f>
         <v>2438</v>
       </c>
-      <c r="AX54" s="9">
-        <f>+AX38+AX40</f>
+      <c r="BB54" s="9">
+        <f>+BB38+BB40</f>
         <v>3114</v>
       </c>
-      <c r="AY54" s="9">
-        <f>+AY38+AY40</f>
+      <c r="BC54" s="9">
+        <f>+BC38+BC40</f>
         <v>-6117</v>
       </c>
-      <c r="AZ54" s="9">
+      <c r="BD54" s="9">
         <f>SUM(J54:L54)</f>
         <v>-164</v>
       </c>
     </row>
-    <row r="55" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>118</v>
       </c>
-      <c r="AI55" s="2">
-        <f t="shared" ref="AI55" si="18">+AI54+AH54</f>
+      <c r="AM55" s="2">
+        <f t="shared" ref="AM55" si="47">+AM54+AL54</f>
         <v>-2012</v>
       </c>
-      <c r="AJ55" s="2">
-        <f t="shared" ref="AJ55" si="19">+AJ54+AI54</f>
+      <c r="AN55" s="2">
+        <f t="shared" ref="AN55" si="48">+AN54+AM54</f>
         <v>-4177</v>
       </c>
-      <c r="AK55" s="2">
-        <f t="shared" ref="AK55" si="20">+AK54+AJ54</f>
+      <c r="AO55" s="2">
+        <f t="shared" ref="AO55" si="49">+AO54+AN54</f>
         <v>-793</v>
       </c>
-      <c r="AL55" s="2">
-        <f t="shared" ref="AL55" si="21">+AL54+AK54</f>
+      <c r="AP55" s="2">
+        <f t="shared" ref="AP55" si="50">+AP54+AO54</f>
         <v>3198</v>
       </c>
-      <c r="AM55" s="2">
-        <f t="shared" ref="AM55" si="22">+AM54+AL54</f>
+      <c r="AQ55" s="2">
+        <f t="shared" ref="AQ55" si="51">+AQ54+AP54</f>
         <v>2414</v>
       </c>
-      <c r="AN55" s="2">
-        <f t="shared" ref="AN55:AR55" si="23">+AN54+AM54</f>
+      <c r="AR55" s="2">
+        <f t="shared" ref="AR55:AV55" si="52">+AR54+AQ54</f>
         <v>349</v>
       </c>
-      <c r="AO55" s="2">
-        <f t="shared" si="23"/>
+      <c r="AS55" s="2">
+        <f t="shared" si="52"/>
         <v>784</v>
       </c>
-      <c r="AP55" s="2">
-        <f t="shared" si="23"/>
+      <c r="AT55" s="2">
+        <f t="shared" si="52"/>
         <v>2961</v>
       </c>
-      <c r="AQ55" s="2">
-        <f t="shared" si="23"/>
+      <c r="AU55" s="2">
+        <f t="shared" si="52"/>
         <v>3779</v>
       </c>
-      <c r="AR55" s="2">
-        <f t="shared" si="23"/>
+      <c r="AV55" s="2">
+        <f t="shared" si="52"/>
         <v>-1462</v>
       </c>
-      <c r="AS55" s="2">
-        <f>+AS54+AR54</f>
+      <c r="AW55" s="2">
+        <f t="shared" ref="AW55:BD55" si="53">+AW54+AV54</f>
         <v>770</v>
       </c>
-      <c r="AT55" s="2">
-        <f>+AT54+AS54</f>
+      <c r="AX55" s="2">
+        <f t="shared" si="53"/>
         <v>11940</v>
       </c>
-      <c r="AU55" s="2">
-        <f>+AU54+AT54</f>
+      <c r="AY55" s="2">
+        <f t="shared" si="53"/>
         <v>11930</v>
       </c>
-      <c r="AV55" s="2">
-        <f>+AV54+AU54</f>
+      <c r="AZ55" s="2">
+        <f t="shared" si="53"/>
         <v>3492</v>
       </c>
-      <c r="AW55" s="2">
-        <f>+AW54+AV54</f>
+      <c r="BA55" s="2">
+        <f t="shared" si="53"/>
         <v>2521</v>
       </c>
-      <c r="AX55" s="2">
-        <f>+AX54+AW54</f>
+      <c r="BB55" s="2">
+        <f t="shared" si="53"/>
         <v>5552</v>
       </c>
-      <c r="AY55" s="2">
-        <f>+AY54+AX54</f>
+      <c r="BC55" s="2">
+        <f t="shared" si="53"/>
         <v>-3003</v>
       </c>
-      <c r="AZ55" s="2">
-        <f>+AZ54+AY54</f>
+      <c r="BD55" s="2">
+        <f t="shared" si="53"/>
         <v>-6281</v>
       </c>
     </row>
-    <row r="56" spans="2:52" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="22" t="s">
+    <row r="56" spans="2:56" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="23"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="23"/>
-      <c r="M56" s="23"/>
-      <c r="N56" s="23"/>
-      <c r="AJ56" s="13">
-        <f t="shared" ref="AJ56" si="24">SUM(AH54:AJ54)</f>
+      <c r="AN56" s="2">
+        <f t="shared" ref="AN56" si="54">SUM(AL54:AN54)</f>
         <v>-3523</v>
       </c>
-      <c r="AK56" s="13">
-        <f>SUM(AI54:AK54)</f>
+      <c r="AO56" s="2">
+        <f>SUM(AM54:AO54)</f>
         <v>-3459</v>
       </c>
-      <c r="AL56" s="13">
-        <f t="shared" ref="AL56" si="25">SUM(AJ54:AL54)</f>
+      <c r="AP56" s="2">
+        <f t="shared" ref="AP56" si="55">SUM(AN54:AP54)</f>
         <v>1687</v>
       </c>
-      <c r="AM56" s="13">
-        <f t="shared" ref="AM56" si="26">SUM(AK54:AM54)</f>
+      <c r="AQ56" s="2">
+        <f t="shared" ref="AQ56" si="56">SUM(AO54:AQ54)</f>
         <v>3132</v>
       </c>
-      <c r="AN56" s="13">
-        <f t="shared" ref="AN56" si="27">SUM(AL54:AN54)</f>
+      <c r="AR56" s="2">
+        <f t="shared" ref="AR56" si="57">SUM(AP54:AR54)</f>
         <v>2829</v>
       </c>
-      <c r="AO56" s="13">
-        <f t="shared" ref="AO56:AS56" si="28">SUM(AM54:AO54)</f>
+      <c r="AS56" s="2">
+        <f t="shared" ref="AS56:AW56" si="58">SUM(AQ54:AS54)</f>
         <v>718</v>
       </c>
-      <c r="AP56" s="13">
-        <f t="shared" si="28"/>
+      <c r="AT56" s="2">
+        <f t="shared" si="58"/>
         <v>3376</v>
       </c>
-      <c r="AQ56" s="13">
-        <f t="shared" si="28"/>
+      <c r="AU56" s="2">
+        <f t="shared" si="58"/>
         <v>4148</v>
       </c>
-      <c r="AR56" s="13">
-        <f t="shared" si="28"/>
+      <c r="AV56" s="2">
+        <f t="shared" si="58"/>
         <v>1130</v>
       </c>
-      <c r="AS56" s="13">
-        <f t="shared" si="28"/>
+      <c r="AW56" s="2">
+        <f t="shared" si="58"/>
         <v>1957</v>
       </c>
-      <c r="AT56" s="13">
-        <f>SUM(AR54:AT54)</f>
+      <c r="AX56" s="2">
+        <f t="shared" ref="AX56:BD56" si="59">SUM(AV54:AX54)</f>
         <v>9291</v>
       </c>
-      <c r="AU56" s="13">
-        <f>SUM(AS54:AU54)</f>
+      <c r="AY56" s="2">
+        <f t="shared" si="59"/>
         <v>15349</v>
       </c>
-      <c r="AV56" s="13">
-        <f>SUM(AT54:AV54)</f>
+      <c r="AZ56" s="2">
+        <f t="shared" si="59"/>
         <v>12013</v>
       </c>
-      <c r="AW56" s="13">
-        <f>SUM(AU54:AW54)</f>
+      <c r="BA56" s="2">
+        <f t="shared" si="59"/>
         <v>5930</v>
       </c>
-      <c r="AX56" s="13">
-        <f>SUM(AV54:AX54)</f>
+      <c r="BB56" s="2">
+        <f t="shared" si="59"/>
         <v>5635</v>
       </c>
-      <c r="AY56" s="13">
-        <f>SUM(AW54:AY54)</f>
+      <c r="BC56" s="2">
+        <f t="shared" si="59"/>
         <v>-565</v>
       </c>
-      <c r="AZ56" s="13">
-        <f>SUM(AX54:AZ54)</f>
+      <c r="BD56" s="2">
+        <f t="shared" si="59"/>
         <v>-3167</v>
       </c>
     </row>
-    <row r="57" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>120</v>
       </c>
-      <c r="AK57" s="2">
-        <f t="shared" ref="AK57" si="29">SUM(AH54:AK54)</f>
+      <c r="AO57" s="2">
+        <f t="shared" ref="AO57" si="60">SUM(AL54:AO54)</f>
         <v>-2805</v>
       </c>
-      <c r="AL57" s="2">
-        <f t="shared" ref="AL57" si="30">SUM(AI54:AL54)</f>
+      <c r="AP57" s="2">
+        <f t="shared" ref="AP57" si="61">SUM(AM54:AP54)</f>
         <v>-979</v>
       </c>
-      <c r="AM57" s="2">
-        <f t="shared" ref="AM57" si="31">SUM(AJ54:AM54)</f>
+      <c r="AQ57" s="2">
+        <f t="shared" ref="AQ57" si="62">SUM(AN54:AQ54)</f>
         <v>1621</v>
       </c>
-      <c r="AN57" s="2">
-        <f t="shared" ref="AN57" si="32">SUM(AK54:AN54)</f>
+      <c r="AR57" s="2">
+        <f t="shared" ref="AR57" si="63">SUM(AO54:AR54)</f>
         <v>3547</v>
       </c>
-      <c r="AO57" s="2">
-        <f t="shared" ref="AO57" si="33">SUM(AL54:AO54)</f>
+      <c r="AS57" s="2">
+        <f t="shared" ref="AS57" si="64">SUM(AP54:AS54)</f>
         <v>3198</v>
       </c>
-      <c r="AP57" s="2">
-        <f t="shared" ref="AP57:AT57" si="34">SUM(AM54:AP54)</f>
+      <c r="AT57" s="2">
+        <f t="shared" ref="AT57:AX57" si="65">SUM(AQ54:AT54)</f>
         <v>3310</v>
       </c>
-      <c r="AQ57" s="2">
-        <f t="shared" si="34"/>
+      <c r="AU57" s="2">
+        <f t="shared" si="65"/>
         <v>4563</v>
       </c>
-      <c r="AR57" s="2">
-        <f t="shared" si="34"/>
+      <c r="AV57" s="2">
+        <f t="shared" si="65"/>
         <v>1499</v>
       </c>
-      <c r="AS57" s="2">
-        <f t="shared" si="34"/>
+      <c r="AW57" s="2">
+        <f t="shared" si="65"/>
         <v>4549</v>
       </c>
-      <c r="AT57" s="2">
-        <f t="shared" si="34"/>
+      <c r="AX57" s="2">
+        <f t="shared" si="65"/>
         <v>10478</v>
       </c>
-      <c r="AU57" s="2">
-        <f>SUM(AR54:AU54)</f>
+      <c r="AY57" s="2">
+        <f t="shared" ref="AY57:BD57" si="66">SUM(AV54:AY54)</f>
         <v>12700</v>
       </c>
-      <c r="AV57" s="2">
-        <f>SUM(AS54:AV54)</f>
+      <c r="AZ57" s="2">
+        <f t="shared" si="66"/>
         <v>15432</v>
       </c>
-      <c r="AW57" s="2">
-        <f>SUM(AT54:AW54)</f>
+      <c r="BA57" s="2">
+        <f t="shared" si="66"/>
         <v>14451</v>
       </c>
-      <c r="AX57" s="2">
-        <f>SUM(AU54:AX54)</f>
+      <c r="BB57" s="2">
+        <f t="shared" si="66"/>
         <v>9044</v>
       </c>
-      <c r="AY57" s="2">
-        <f>SUM(AV54:AY54)</f>
+      <c r="BC57" s="2">
+        <f t="shared" si="66"/>
         <v>-482</v>
       </c>
-      <c r="AZ57" s="2">
-        <f>SUM(AW54:AZ54)</f>
+      <c r="BD57" s="2">
+        <f t="shared" si="66"/>
         <v>-729</v>
       </c>
     </row>
-    <row r="58" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>121</v>
       </c>
-      <c r="AL58" s="13">
-        <f t="shared" ref="AL58" si="35">SUM(AH54:AL54)</f>
+      <c r="AP58" s="2">
+        <f t="shared" ref="AP58" si="67">SUM(AL54:AP54)</f>
         <v>-325</v>
       </c>
-      <c r="AM58" s="13">
-        <f t="shared" ref="AM58" si="36">SUM(AI54:AM54)</f>
+      <c r="AQ58" s="2">
+        <f t="shared" ref="AQ58" si="68">SUM(AM54:AQ54)</f>
         <v>-1045</v>
       </c>
-      <c r="AN58" s="13">
-        <f t="shared" ref="AN58" si="37">SUM(AJ54:AN54)</f>
+      <c r="AR58" s="2">
+        <f t="shared" ref="AR58" si="69">SUM(AN54:AR54)</f>
         <v>2036</v>
       </c>
-      <c r="AO58" s="13">
-        <f t="shared" ref="AO58" si="38">SUM(AK54:AO54)</f>
+      <c r="AS58" s="2">
+        <f t="shared" ref="AS58" si="70">SUM(AO54:AS54)</f>
         <v>3916</v>
       </c>
-      <c r="AP58" s="13">
-        <f t="shared" ref="AP58" si="39">SUM(AL54:AP54)</f>
+      <c r="AT58" s="2">
+        <f t="shared" ref="AT58" si="71">SUM(AP54:AT54)</f>
         <v>5790</v>
       </c>
-      <c r="AQ58" s="13">
-        <f t="shared" ref="AQ58:AU58" si="40">SUM(AM54:AQ54)</f>
+      <c r="AU58" s="2">
+        <f t="shared" ref="AU58:AY58" si="72">SUM(AQ54:AU54)</f>
         <v>4497</v>
       </c>
-      <c r="AR58" s="13">
-        <f t="shared" si="40"/>
+      <c r="AV58" s="2">
+        <f t="shared" si="72"/>
         <v>1914</v>
       </c>
-      <c r="AS58" s="13">
-        <f t="shared" si="40"/>
+      <c r="AW58" s="2">
+        <f t="shared" si="72"/>
         <v>4918</v>
       </c>
-      <c r="AT58" s="13">
-        <f t="shared" si="40"/>
+      <c r="AX58" s="2">
+        <f t="shared" si="72"/>
         <v>13070</v>
       </c>
-      <c r="AU58" s="13">
-        <f t="shared" si="40"/>
+      <c r="AY58" s="2">
+        <f t="shared" si="72"/>
         <v>13887</v>
-      </c>
-      <c r="AV58" s="13">
-        <f>SUM(AR54:AV54)</f>
-        <v>12783</v>
-      </c>
-      <c r="AW58" s="13">
-        <f>SUM(AS54:AW54)</f>
-        <v>17870</v>
-      </c>
-      <c r="AX58" s="13">
-        <f>SUM(AT54:AX54)</f>
-        <v>17565</v>
-      </c>
-      <c r="AY58" s="2">
-        <f>SUM(AU54:AY54)</f>
-        <v>2927</v>
       </c>
       <c r="AZ58" s="2">
         <f>SUM(AV54:AZ54)</f>
+        <v>12783</v>
+      </c>
+      <c r="BA58" s="2">
+        <f>SUM(AW54:BA54)</f>
+        <v>17870</v>
+      </c>
+      <c r="BB58" s="2">
+        <f>SUM(AX54:BB54)</f>
+        <v>17565</v>
+      </c>
+      <c r="BC58" s="2">
+        <f>SUM(AY54:BC54)</f>
+        <v>2927</v>
+      </c>
+      <c r="BD58" s="2">
+        <f>SUM(AZ54:BD54)</f>
         <v>-646</v>
       </c>
     </row>
-    <row r="59" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>122</v>
       </c>
-      <c r="AM59" s="2">
-        <f t="shared" ref="AM59" si="41">SUM(AH54:AM54)</f>
+      <c r="AQ59" s="2">
+        <f t="shared" ref="AQ59" si="73">SUM(AL54:AQ54)</f>
         <v>-391</v>
       </c>
-      <c r="AN59" s="2">
-        <f t="shared" ref="AN59" si="42">SUM(AI54:AN54)</f>
+      <c r="AR59" s="2">
+        <f t="shared" ref="AR59" si="74">SUM(AM54:AR54)</f>
         <v>-630</v>
       </c>
-      <c r="AO59" s="2">
-        <f t="shared" ref="AO59" si="43">SUM(AJ54:AO54)</f>
+      <c r="AS59" s="2">
+        <f t="shared" ref="AS59" si="75">SUM(AN54:AS54)</f>
         <v>2405</v>
       </c>
-      <c r="AP59" s="2">
-        <f t="shared" ref="AP59" si="44">SUM(AK54:AP54)</f>
+      <c r="AT59" s="2">
+        <f t="shared" ref="AT59" si="76">SUM(AO54:AT54)</f>
         <v>6508</v>
       </c>
-      <c r="AQ59" s="2">
-        <f t="shared" ref="AQ59" si="45">SUM(AL54:AQ54)</f>
+      <c r="AU59" s="2">
+        <f t="shared" ref="AU59" si="77">SUM(AP54:AU54)</f>
         <v>6977</v>
       </c>
-      <c r="AR59" s="2">
-        <f t="shared" ref="AR59:AV59" si="46">SUM(AM54:AR54)</f>
+      <c r="AV59" s="2">
+        <f t="shared" ref="AV59:AZ59" si="78">SUM(AQ54:AV54)</f>
         <v>1848</v>
       </c>
-      <c r="AS59" s="2">
-        <f t="shared" si="46"/>
+      <c r="AW59" s="2">
+        <f t="shared" si="78"/>
         <v>5333</v>
       </c>
-      <c r="AT59" s="2">
-        <f t="shared" si="46"/>
+      <c r="AX59" s="2">
+        <f t="shared" si="78"/>
         <v>13439</v>
       </c>
-      <c r="AU59" s="2">
-        <f t="shared" si="46"/>
+      <c r="AY59" s="2">
+        <f t="shared" si="78"/>
         <v>16479</v>
       </c>
-      <c r="AV59" s="2">
-        <f t="shared" si="46"/>
+      <c r="AZ59" s="2">
+        <f t="shared" si="78"/>
         <v>13970</v>
       </c>
-      <c r="AW59" s="2">
-        <f>SUM(AR54:AW54)</f>
+      <c r="BA59" s="2">
+        <f>SUM(AV54:BA54)</f>
         <v>15221</v>
       </c>
-      <c r="AX59" s="2">
-        <f>SUM(AS54:AX54)</f>
+      <c r="BB59" s="2">
+        <f>SUM(AW54:BB54)</f>
         <v>20984</v>
       </c>
-      <c r="AY59" s="2">
-        <f>SUM(AT54:AY54)</f>
+      <c r="BC59" s="2">
+        <f>SUM(AX54:BC54)</f>
         <v>11448</v>
       </c>
-      <c r="AZ59" s="2">
-        <f>SUM(AU54:AZ54)</f>
+      <c r="BD59" s="2">
+        <f>SUM(AY54:BD54)</f>
         <v>2763</v>
       </c>
     </row>
-    <row r="60" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>124</v>
       </c>
-      <c r="AN60" s="2">
-        <f t="shared" ref="AN60" si="47">SUM(AH54:AN54)</f>
+      <c r="AR60" s="2">
+        <f t="shared" ref="AR60" si="79">SUM(AL54:AR54)</f>
         <v>24</v>
       </c>
-      <c r="AO60" s="2">
-        <f t="shared" ref="AO60" si="48">SUM(AI54:AO54)</f>
+      <c r="AS60" s="2">
+        <f t="shared" ref="AS60" si="80">SUM(AM54:AS54)</f>
         <v>-261</v>
       </c>
-      <c r="AP60" s="2">
-        <f t="shared" ref="AP60" si="49">SUM(AJ54:AP54)</f>
+      <c r="AT60" s="2">
+        <f t="shared" ref="AT60" si="81">SUM(AN54:AT54)</f>
         <v>4997</v>
       </c>
-      <c r="AQ60" s="2">
-        <f t="shared" ref="AQ60" si="50">SUM(AK54:AQ54)</f>
+      <c r="AU60" s="2">
+        <f t="shared" ref="AU60" si="82">SUM(AO54:AU54)</f>
         <v>7695</v>
       </c>
-      <c r="AR60" s="2">
-        <f t="shared" ref="AR60" si="51">SUM(AL54:AR54)</f>
+      <c r="AV60" s="2">
+        <f t="shared" ref="AV60" si="83">SUM(AP54:AV54)</f>
         <v>4328</v>
       </c>
-      <c r="AS60" s="2">
-        <f t="shared" ref="AS60:AW60" si="52">SUM(AM54:AS54)</f>
+      <c r="AW60" s="2">
+        <f t="shared" ref="AW60:BA60" si="84">SUM(AQ54:AW54)</f>
         <v>5267</v>
       </c>
-      <c r="AT60" s="2">
-        <f t="shared" si="52"/>
+      <c r="AX60" s="2">
+        <f t="shared" si="84"/>
         <v>13854</v>
       </c>
-      <c r="AU60" s="2">
-        <f t="shared" si="52"/>
+      <c r="AY60" s="2">
+        <f t="shared" si="84"/>
         <v>16848</v>
       </c>
-      <c r="AV60" s="2">
-        <f t="shared" si="52"/>
+      <c r="AZ60" s="2">
+        <f t="shared" si="84"/>
         <v>16562</v>
       </c>
-      <c r="AW60" s="2">
-        <f t="shared" si="52"/>
+      <c r="BA60" s="2">
+        <f t="shared" si="84"/>
         <v>16408</v>
       </c>
-      <c r="AX60" s="2">
-        <f>SUM(AR54:AX54)</f>
+      <c r="BB60" s="2">
+        <f>SUM(AV54:BB54)</f>
         <v>18335</v>
       </c>
-      <c r="AY60" s="2">
-        <f>SUM(AS54:AY54)</f>
+      <c r="BC60" s="2">
+        <f>SUM(AW54:BC54)</f>
         <v>14867</v>
       </c>
-      <c r="AZ60" s="2">
-        <f>SUM(AT54:AZ54)</f>
+      <c r="BD60" s="2">
+        <f>SUM(AX54:BD54)</f>
         <v>11284</v>
       </c>
     </row>
-    <row r="63" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:56" ht="13" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>125</v>
       </c>
-      <c r="S63" s="24">
+      <c r="W63" s="20">
         <v>1.4125000000000001</v>
       </c>
-      <c r="T63" s="1">
+      <c r="X63" s="1">
         <v>1.8875</v>
       </c>
-      <c r="U63" s="1">
+      <c r="Y63" s="1">
         <v>4.6500000000000004</v>
       </c>
-      <c r="V63" s="1">
+      <c r="Z63" s="1">
         <v>11.0313</v>
       </c>
-      <c r="W63" s="1">
+      <c r="AA63" s="1">
         <v>19.809999999999999</v>
       </c>
-      <c r="X63" s="1">
+      <c r="AB63" s="1">
         <v>14.56</v>
       </c>
-      <c r="Y63">
+      <c r="AC63">
         <v>12.97</v>
       </c>
-      <c r="Z63">
+      <c r="AD63">
         <v>25.28</v>
       </c>
-      <c r="AA63" s="20">
+      <c r="AE63" s="18">
         <v>39.06</v>
       </c>
-      <c r="AB63" s="24">
+      <c r="AF63" s="20">
         <v>35.5</v>
       </c>
-      <c r="AC63" s="24">
+      <c r="AG63" s="20">
         <v>31</v>
       </c>
-      <c r="AD63" s="24">
+      <c r="AH63" s="20">
         <v>9.74</v>
       </c>
-      <c r="AE63" s="20">
+      <c r="AI63" s="18">
         <v>13.47</v>
       </c>
-      <c r="AF63" s="20">
+      <c r="AJ63" s="18">
         <v>12.35</v>
       </c>
-      <c r="AG63" s="20">
+      <c r="AK63" s="18">
         <v>13.31</v>
       </c>
-      <c r="AH63" s="20">
+      <c r="AL63" s="18">
         <v>13.96</v>
       </c>
-      <c r="AI63" s="20">
+      <c r="AM63" s="18">
         <v>7.25</v>
       </c>
-      <c r="AJ63" s="20">
+      <c r="AN63" s="18">
         <v>2.64</v>
       </c>
-      <c r="AK63">
+      <c r="AO63">
         <v>10.56</v>
       </c>
-      <c r="AL63">
+      <c r="AP63">
         <v>8.02</v>
       </c>
-      <c r="AM63">
+      <c r="AQ63">
         <v>6.29</v>
       </c>
-      <c r="AN63">
+      <c r="AR63">
         <v>6.34</v>
       </c>
-      <c r="AO63">
+      <c r="AS63">
         <v>21.75</v>
       </c>
-      <c r="AP63">
+      <c r="AT63">
         <v>35.01</v>
       </c>
-      <c r="AQ63">
+      <c r="AU63">
         <v>14.16</v>
       </c>
-      <c r="AR63" s="3">
+      <c r="AV63" s="3">
         <v>21.92</v>
       </c>
-      <c r="AS63">
+      <c r="AW63">
         <v>41.12</v>
       </c>
-      <c r="AT63">
+      <c r="AX63">
         <v>31.73</v>
       </c>
-      <c r="AU63">
+      <c r="AY63">
         <v>53.78</v>
       </c>
-      <c r="AV63">
+      <c r="AZ63">
         <v>75.180000000000007</v>
       </c>
-      <c r="AW63">
+      <c r="BA63">
         <v>93.15</v>
       </c>
-      <c r="AX63">
+      <c r="BB63">
         <v>49.98</v>
       </c>
-      <c r="AY63" s="1">
+      <c r="BC63" s="1">
         <v>85.34</v>
       </c>
-      <c r="AZ63" s="1">
+      <c r="BD63" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>152</v>
       </c>
-      <c r="AD65" s="2">
-        <f>AD10/AD63</f>
+      <c r="AH65" s="2">
+        <f>AH10/AH63</f>
         <v>265.81108829568785</v>
       </c>
-      <c r="AE65" s="2">
-        <f t="shared" ref="AE65:AZ65" si="53">AE10/AE63</f>
+      <c r="AI65" s="2">
+        <f t="shared" ref="AI65:BD65" si="85">AI10/AI63</f>
         <v>229.47290274684482</v>
       </c>
-      <c r="AF65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AJ65" s="2">
+        <f t="shared" si="85"/>
         <v>356.59919028340084</v>
       </c>
-      <c r="AG65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AK65" s="2">
+        <f t="shared" si="85"/>
         <v>366.64162283996995</v>
       </c>
-      <c r="AH65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AL65" s="2">
+        <f t="shared" si="85"/>
         <v>377.65042979942689</v>
       </c>
-      <c r="AI65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AM65" s="2">
+        <f t="shared" si="85"/>
         <v>784.55172413793105</v>
       </c>
-      <c r="AJ65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AN65" s="2">
+        <f t="shared" si="85"/>
         <v>2212.5</v>
       </c>
-      <c r="AK65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AO65" s="2">
+        <f t="shared" si="85"/>
         <v>454.82954545454544</v>
       </c>
-      <c r="AL65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AP65" s="2">
+        <f t="shared" si="85"/>
         <v>1057.6059850374065</v>
       </c>
-      <c r="AM65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AQ65" s="2">
+        <f t="shared" si="85"/>
         <v>1397.1383147853735</v>
       </c>
-      <c r="AN65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AR65" s="2">
+        <f t="shared" si="85"/>
         <v>1298.7381703470032</v>
       </c>
-      <c r="AO65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AS65" s="2">
+        <f t="shared" si="85"/>
         <v>417.14942528735634</v>
       </c>
-      <c r="AP65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AT65" s="2">
+        <f t="shared" si="85"/>
         <v>467.23793201942306</v>
       </c>
-      <c r="AQ65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AU65" s="2">
+        <f t="shared" si="85"/>
         <v>1143.5028248587571</v>
       </c>
-      <c r="AR65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AV65" s="2">
+        <f t="shared" si="85"/>
         <v>565.64781021897807</v>
       </c>
-      <c r="AS65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AW65" s="2">
+        <f t="shared" si="85"/>
         <v>494.21206225680936</v>
       </c>
-      <c r="AT65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AX65" s="2">
+        <f t="shared" si="85"/>
         <v>957.80018909549324</v>
       </c>
-      <c r="AU65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AY65" s="2">
+        <f t="shared" si="85"/>
         <v>435.21755299367794</v>
       </c>
-      <c r="AV65" s="2">
-        <f t="shared" si="53"/>
+      <c r="AZ65" s="2">
+        <f t="shared" si="85"/>
         <v>285.11572226656023</v>
       </c>
-      <c r="AW65" s="2">
-        <f t="shared" si="53"/>
+      <c r="BA65" s="2">
+        <f t="shared" si="85"/>
         <v>297.42351046698872</v>
       </c>
-      <c r="AX65" s="2">
-        <f t="shared" si="53"/>
+      <c r="BB65" s="2">
+        <f t="shared" si="85"/>
         <v>615.40616246498598</v>
       </c>
-      <c r="AY65" s="2">
-        <f t="shared" si="53"/>
+      <c r="BC65" s="2">
+        <f t="shared" si="85"/>
         <v>182.09514881649869</v>
       </c>
-      <c r="AZ65" s="2">
-        <f t="shared" si="53"/>
-        <v>277.34444444444443</v>
+      <c r="BD65" s="2">
+        <f t="shared" si="85"/>
+        <v>279.01111111111112</v>
       </c>
     </row>
-    <row r="66" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="AD66" s="2"/>
+    <row r="66" spans="2:56" x14ac:dyDescent="0.25">
+      <c r="AH66" s="2"/>
     </row>
-    <row r="67" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="AB67" s="20" t="s">
+    <row r="67" spans="2:56" ht="13" x14ac:dyDescent="0.3">
+      <c r="AF67" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="AD67" s="24">
-        <f>CORREL(AD63:AZ63,AD10:AZ10)</f>
-        <v>0.75122759643426718</v>
+      <c r="AH67" s="20">
+        <f>CORREL(AH63:BD63,AH10:BD10)</f>
+        <v>0.75201470810792281</v>
       </c>
     </row>
-    <row r="68" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="AB68" s="20" t="s">
+    <row r="68" spans="2:56" ht="13" x14ac:dyDescent="0.3">
+      <c r="AF68" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="AD68" s="24">
-        <f>CORREL(AF63:AZ63,AF54:AZ54)</f>
+      <c r="AH68" s="20">
+        <f>CORREL(AJ63:BD63,AJ54:BD54)</f>
         <v>-7.7804094292837064E-2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{8500311A-A2A0-4708-A1FC-B4D34FF7D086}"/>
   </hyperlinks>
